--- a/GameData/DataSheet.xlsx
+++ b/GameData/DataSheet.xlsx
@@ -9,6 +9,7 @@
     <sheet name="광물" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="상점목록" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="업적" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="몬스터" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Arial"/>
       <color rgb="FF000000"/>
@@ -43,8 +44,12 @@
       <color rgb="00555555"/>
       <sz val="9"/>
     </font>
+    <font>
+      <i val="1"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -61,8 +66,23 @@
         <fgColor rgb="004A7C59"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F4E8"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="7">
+  <borders count="12">
     <border/>
     <border>
       <left style="thin">
@@ -109,11 +129,57 @@
         <color rgb="00AAAAAA"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00CCCCCC"/>
+      </left>
+      <right style="thin">
+        <color rgb="00CCCCCC"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CCCCCC"/>
+      </bottom>
+    </border>
+    <border>
+      <top style="thin">
+        <color rgb="00CCCCCC"/>
+      </top>
+    </border>
+    <border>
+      <right style="thin">
+        <color rgb="00CCCCCC"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CCCCCC"/>
+      </top>
+    </border>
+    <border>
+      <top style="thin">
+        <color rgb="00CCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CCCCCC"/>
+      </bottom>
+    </border>
+    <border>
+      <right style="thin">
+        <color rgb="00CCCCCC"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CCCCCC"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -142,6 +208,29 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4111,4 +4200,632 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:P14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" style="8" min="1" max="1"/>
+    <col width="14" customWidth="1" style="8" min="2" max="2"/>
+    <col width="18" customWidth="1" style="8" min="3" max="3"/>
+    <col width="12" customWidth="1" style="8" min="4" max="4"/>
+    <col width="8" customWidth="1" style="8" min="5" max="5"/>
+    <col width="10" customWidth="1" style="8" min="6" max="6"/>
+    <col width="10" customWidth="1" style="8" min="7" max="7"/>
+    <col width="12" customWidth="1" style="8" min="8" max="8"/>
+    <col width="12" customWidth="1" style="8" min="9" max="9"/>
+    <col width="8" customWidth="1" style="8" min="10" max="10"/>
+    <col width="12" customWidth="1" style="8" min="11" max="11"/>
+    <col width="40" customWidth="1" style="8" min="12" max="12"/>
+    <col width="12" customWidth="1" style="8" min="13" max="13"/>
+    <col width="12" customWidth="1" style="8" min="14" max="14"/>
+    <col width="14" customWidth="1" style="8" min="15" max="15"/>
+    <col width="12" customWidth="1" style="8" min="16" max="16"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1" s="8">
+      <c r="A1" s="16" t="inlineStr">
+        <is>
+          <t>MonsterID</t>
+        </is>
+      </c>
+      <c r="B1" s="16" t="inlineStr">
+        <is>
+          <t>이름(KO)</t>
+        </is>
+      </c>
+      <c r="C1" s="16" t="inlineStr">
+        <is>
+          <t>이름(EN)</t>
+        </is>
+      </c>
+      <c r="D1" s="16" t="inlineStr">
+        <is>
+          <t>monsterType</t>
+        </is>
+      </c>
+      <c r="E1" s="16" t="inlineStr">
+        <is>
+          <t>기본HP</t>
+        </is>
+      </c>
+      <c r="F1" s="16" t="inlineStr">
+        <is>
+          <t>HP/난이도</t>
+        </is>
+      </c>
+      <c r="G1" s="16" t="inlineStr">
+        <is>
+          <t>기본데미지</t>
+        </is>
+      </c>
+      <c r="H1" s="16" t="inlineStr">
+        <is>
+          <t>데미지/난이도</t>
+        </is>
+      </c>
+      <c r="I1" s="16" t="inlineStr">
+        <is>
+          <t>공격간격(s)</t>
+        </is>
+      </c>
+      <c r="J1" s="16" t="inlineStr">
+        <is>
+          <t>스폰수</t>
+        </is>
+      </c>
+      <c r="K1" s="16" t="inlineStr">
+        <is>
+          <t>초기딜레이</t>
+        </is>
+      </c>
+      <c r="L1" s="16" t="inlineStr">
+        <is>
+          <t>특수효과</t>
+        </is>
+      </c>
+      <c r="M1" s="16" t="inlineStr">
+        <is>
+          <t>D0-49 가중치</t>
+        </is>
+      </c>
+      <c r="N1" s="16" t="inlineStr">
+        <is>
+          <t>D50-99 가중치</t>
+        </is>
+      </c>
+      <c r="O1" s="16" t="inlineStr">
+        <is>
+          <t>D100-199 가중치</t>
+        </is>
+      </c>
+      <c r="P1" s="16" t="inlineStr">
+        <is>
+          <t>D200+ 가중치</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="17" t="inlineStr">
+        <is>
+          <t>[일반 몬스터 - SpawnTable 등록]</t>
+        </is>
+      </c>
+      <c r="B2" s="18" t="n"/>
+      <c r="C2" s="18" t="n"/>
+      <c r="D2" s="18" t="n"/>
+      <c r="E2" s="18" t="n"/>
+      <c r="F2" s="18" t="n"/>
+      <c r="G2" s="18" t="n"/>
+      <c r="H2" s="18" t="n"/>
+      <c r="I2" s="18" t="n"/>
+      <c r="J2" s="18" t="n"/>
+      <c r="K2" s="18" t="n"/>
+      <c r="L2" s="18" t="n"/>
+      <c r="M2" s="18" t="n"/>
+      <c r="N2" s="18" t="n"/>
+      <c r="O2" s="18" t="n"/>
+      <c r="P2" s="19" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="20" t="inlineStr">
+        <is>
+          <t>Combat_Monster_Rat</t>
+        </is>
+      </c>
+      <c r="B3" s="20" t="inlineStr">
+        <is>
+          <t>동굴쥐</t>
+        </is>
+      </c>
+      <c r="C3" s="20" t="inlineStr">
+        <is>
+          <t>Cave Rat</t>
+        </is>
+      </c>
+      <c r="D3" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="F3" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H3" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" s="21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L3" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M3" s="21" t="n">
+        <v>50</v>
+      </c>
+      <c r="N3" s="21" t="n">
+        <v>25</v>
+      </c>
+      <c r="O3" s="21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P3" s="21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="22" t="inlineStr">
+        <is>
+          <t>Combat_Monster_Spider</t>
+        </is>
+      </c>
+      <c r="B4" s="22" t="inlineStr">
+        <is>
+          <t>동굴거미</t>
+        </is>
+      </c>
+      <c r="C4" s="22" t="inlineStr">
+        <is>
+          <t>Cave Spider</t>
+        </is>
+      </c>
+      <c r="D4" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="23" t="n">
+        <v>2</v>
+      </c>
+      <c r="H4" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" s="23" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J4" s="23" t="n">
+        <v>3</v>
+      </c>
+      <c r="K4" s="23" t="inlineStr">
+        <is>
+          <t>0.5~1.0s</t>
+        </is>
+      </c>
+      <c r="L4" s="22" t="inlineStr">
+        <is>
+          <t>3마리 동시 스폰, 위치 오프셋 적용</t>
+        </is>
+      </c>
+      <c r="M4" s="23" t="n">
+        <v>30</v>
+      </c>
+      <c r="N4" s="23" t="n">
+        <v>25</v>
+      </c>
+      <c r="O4" s="23" t="n">
+        <v>15</v>
+      </c>
+      <c r="P4" s="23" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="20" t="inlineStr">
+        <is>
+          <t>Combat_Monster_Slime</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>슬라임</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>Slime</t>
+        </is>
+      </c>
+      <c r="D5" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="F5" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H5" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J5" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" s="21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L5" s="20" t="inlineStr">
+        <is>
+          <t>사망 시 SmallSlime ×2 분열</t>
+        </is>
+      </c>
+      <c r="M5" s="21" t="n">
+        <v>20</v>
+      </c>
+      <c r="N5" s="21" t="n">
+        <v>30</v>
+      </c>
+      <c r="O5" s="21" t="n">
+        <v>20</v>
+      </c>
+      <c r="P5" s="21" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="22" t="inlineStr">
+        <is>
+          <t>Combat_Monster_Skeleton</t>
+        </is>
+      </c>
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>해골</t>
+        </is>
+      </c>
+      <c r="C6" s="22" t="inlineStr">
+        <is>
+          <t>Skeleton</t>
+        </is>
+      </c>
+      <c r="D6" s="23" t="n">
+        <v>4</v>
+      </c>
+      <c r="E6" s="23" t="n">
+        <v>4</v>
+      </c>
+      <c r="F6" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" s="23" t="n">
+        <v>2</v>
+      </c>
+      <c r="H6" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" s="23" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J6" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" s="23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L6" s="22" t="inlineStr">
+        <is>
+          <t>사망 시 25% 확률 채굴력 감소 디버프</t>
+        </is>
+      </c>
+      <c r="M6" s="23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N6" s="23" t="n">
+        <v>20</v>
+      </c>
+      <c r="O6" s="23" t="n">
+        <v>30</v>
+      </c>
+      <c r="P6" s="23" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="20" t="inlineStr">
+        <is>
+          <t>Combat_Monster_ArmoredSkeleton</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>중갑해골</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>Armored Skeleton</t>
+        </is>
+      </c>
+      <c r="D7" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="E7" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="F7" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="G7" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="H7" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" s="21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J7" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" s="21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L7" s="20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M7" s="21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N7" s="21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O7" s="21" t="n">
+        <v>25</v>
+      </c>
+      <c r="P7" s="21" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="22" t="inlineStr">
+        <is>
+          <t>Combat_Monster_Mimic</t>
+        </is>
+      </c>
+      <c r="B8" s="22" t="inlineStr">
+        <is>
+          <t>미믹</t>
+        </is>
+      </c>
+      <c r="C8" s="22" t="inlineStr">
+        <is>
+          <t>Mimic</t>
+        </is>
+      </c>
+      <c r="D8" s="23" t="n">
+        <v>6</v>
+      </c>
+      <c r="E8" s="23" t="n">
+        <v>6</v>
+      </c>
+      <c r="F8" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="23" t="n">
+        <v>2</v>
+      </c>
+      <c r="J8" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" s="23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L8" s="22" t="inlineStr">
+        <is>
+          <t>사망 시 MimicRewardTable 랜덤 보상 지급</t>
+        </is>
+      </c>
+      <c r="M8" s="23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N8" s="23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O8" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="P8" s="23" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="17" t="inlineStr">
+        <is>
+          <t>[분열 산물 - Slime 사망 시만 출현]</t>
+        </is>
+      </c>
+      <c r="B9" s="18" t="n"/>
+      <c r="C9" s="18" t="n"/>
+      <c r="D9" s="18" t="n"/>
+      <c r="E9" s="18" t="n"/>
+      <c r="F9" s="18" t="n"/>
+      <c r="G9" s="18" t="n"/>
+      <c r="H9" s="18" t="n"/>
+      <c r="I9" s="18" t="n"/>
+      <c r="J9" s="18" t="n"/>
+      <c r="K9" s="18" t="n"/>
+      <c r="L9" s="18" t="n"/>
+      <c r="M9" s="18" t="n"/>
+      <c r="N9" s="18" t="n"/>
+      <c r="O9" s="18" t="n"/>
+      <c r="P9" s="19" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="20" t="inlineStr">
+        <is>
+          <t>Combat_Monster_SmallSlime</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>작은슬라임</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>Small Slime</t>
+        </is>
+      </c>
+      <c r="D10" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="E10" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="F10" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="21" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J10" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" s="21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L10" s="20" t="inlineStr">
+        <is>
+          <t>Slime 사망 시 분열 산물, SpawnTable 직접 등록 없음</t>
+        </is>
+      </c>
+      <c r="M10" s="21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N10" s="21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O10" s="21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P10" s="21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="24" t="inlineStr">
+        <is>
+          <t>※ 난이도 스케일: depth&lt;50=tier1(+0), depth&lt;100=tier2(+1), depth&lt;200=tier3(+2), depth≥200=tier4(+3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="24" t="inlineStr">
+        <is>
+          <t>※ 최종HP = 기본HP + (HP/난이도 × (tier-1)),  최종데미지 = 기본데미지 + (데미지/난이도 × (tier-1))</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="24" t="inlineStr">
+        <is>
+          <t>※ 가중치 '-' = 해당 구간 미출현</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A13:P13"/>
+    <mergeCell ref="A14:P14"/>
+    <mergeCell ref="A9:P9"/>
+    <mergeCell ref="A12:P12"/>
+    <mergeCell ref="A2:P2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/GameData/DataSheet.xlsx
+++ b/GameData/DataSheet.xlsx
@@ -10,6 +10,7 @@
     <sheet name="상점목록" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="업적" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="몬스터" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="맵_노드" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -4828,4 +4829,431 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" style="8" min="1" max="1"/>
+    <col width="12" customWidth="1" style="8" min="2" max="2"/>
+    <col width="12" customWidth="1" style="8" min="3" max="3"/>
+    <col width="8" customWidth="1" style="8" min="4" max="4"/>
+    <col width="14" customWidth="1" style="8" min="5" max="5"/>
+    <col width="26" customWidth="1" style="8" min="6" max="6"/>
+    <col width="48" customWidth="1" style="8" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1" s="8">
+      <c r="A1" s="16" t="inlineStr">
+        <is>
+          <t>NodeType</t>
+        </is>
+      </c>
+      <c r="B1" s="16" t="inlineStr">
+        <is>
+          <t>표시명(KO)</t>
+        </is>
+      </c>
+      <c r="C1" s="16" t="inlineStr">
+        <is>
+          <t>표시명(EN)</t>
+        </is>
+      </c>
+      <c r="D1" s="16" t="inlineStr">
+        <is>
+          <t>가중치</t>
+        </is>
+      </c>
+      <c r="E1" s="16" t="inlineStr">
+        <is>
+          <t>최초등장 Depth</t>
+        </is>
+      </c>
+      <c r="F1" s="16" t="inlineStr">
+        <is>
+          <t>아이콘 AddressableKey</t>
+        </is>
+      </c>
+      <c r="G1" s="16" t="inlineStr">
+        <is>
+          <t>설명</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="17" t="inlineStr">
+        <is>
+          <t>[노드 타입 목록]</t>
+        </is>
+      </c>
+      <c r="B2" s="18" t="n"/>
+      <c r="C2" s="18" t="n"/>
+      <c r="D2" s="18" t="n"/>
+      <c r="E2" s="18" t="n"/>
+      <c r="F2" s="18" t="n"/>
+      <c r="G2" s="19" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="20" t="inlineStr">
+        <is>
+          <t>Mine</t>
+        </is>
+      </c>
+      <c r="B3" s="20" t="inlineStr">
+        <is>
+          <t>채굴</t>
+        </is>
+      </c>
+      <c r="C3" s="20" t="inlineStr">
+        <is>
+          <t>Mine</t>
+        </is>
+      </c>
+      <c r="D3" s="21" t="n">
+        <v>40</v>
+      </c>
+      <c r="E3" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" s="20" t="inlineStr">
+        <is>
+          <t>Icon_Node_Mine</t>
+        </is>
+      </c>
+      <c r="G3" s="20" t="inlineStr">
+        <is>
+          <t>블록 1개 채굴. 자원 획득.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="22" t="inlineStr">
+        <is>
+          <t>Monster</t>
+        </is>
+      </c>
+      <c r="B4" s="22" t="inlineStr">
+        <is>
+          <t>몬스터</t>
+        </is>
+      </c>
+      <c r="C4" s="22" t="inlineStr">
+        <is>
+          <t>Monster</t>
+        </is>
+      </c>
+      <c r="D4" s="23" t="n">
+        <v>30</v>
+      </c>
+      <c r="E4" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" s="22" t="inlineStr">
+        <is>
+          <t>Icon_Node_Monster</t>
+        </is>
+      </c>
+      <c r="G4" s="22" t="inlineStr">
+        <is>
+          <t>해당 Depth의 SpawnTable 기준 몬스터 전투.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="20" t="inlineStr">
+        <is>
+          <t>Treasure</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>보물</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>Treasure</t>
+        </is>
+      </c>
+      <c r="D5" s="21" t="n">
+        <v>10</v>
+      </c>
+      <c r="E5" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="20" t="inlineStr">
+        <is>
+          <t>Icon_Node_Treasure</t>
+        </is>
+      </c>
+      <c r="G5" s="20" t="inlineStr">
+        <is>
+          <t>랜덤 이벤트(보물 상자). 유물/재화 획득 가능.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="22" t="inlineStr">
+        <is>
+          <t>Grave</t>
+        </is>
+      </c>
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>무덤</t>
+        </is>
+      </c>
+      <c r="C6" s="22" t="inlineStr">
+        <is>
+          <t>Grave</t>
+        </is>
+      </c>
+      <c r="D6" s="23" t="n">
+        <v>8</v>
+      </c>
+      <c r="E6" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="22" t="inlineStr">
+        <is>
+          <t>Icon_Node_Grave</t>
+        </is>
+      </c>
+      <c r="G6" s="22" t="inlineStr">
+        <is>
+          <t>랜덤 이벤트(묘비). Grave Robber 직업 유리.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="20" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>이벤트</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="D7" s="21" t="n">
+        <v>12</v>
+      </c>
+      <c r="E7" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" s="20" t="inlineStr">
+        <is>
+          <t>Icon_Node_Event</t>
+        </is>
+      </c>
+      <c r="G7" s="20" t="inlineStr">
+        <is>
+          <t>랜덤 이벤트(선택지). 보너스 또는 패널티 가능.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="22" t="inlineStr">
+        <is>
+          <t>Boss</t>
+        </is>
+      </c>
+      <c r="B8" s="22" t="inlineStr">
+        <is>
+          <t>보스</t>
+        </is>
+      </c>
+      <c r="C8" s="22" t="inlineStr">
+        <is>
+          <t>Boss</t>
+        </is>
+      </c>
+      <c r="D8" s="23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E8" s="23" t="n">
+        <v>50</v>
+      </c>
+      <c r="F8" s="22" t="inlineStr">
+        <is>
+          <t>Icon_Node_Boss</t>
+        </is>
+      </c>
+      <c r="G8" s="22" t="inlineStr">
+        <is>
+          <t>맵 마지막 Depth(50). 고정 보스 전투.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="17" t="inlineStr">
+        <is>
+          <t>[맵 생성 파라미터 (MapGenerationConfig ScriptableObject)]</t>
+        </is>
+      </c>
+      <c r="B10" s="18" t="n"/>
+      <c r="C10" s="18" t="n"/>
+      <c r="D10" s="18" t="n"/>
+      <c r="E10" s="18" t="n"/>
+      <c r="F10" s="18" t="n"/>
+      <c r="G10" s="19" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="20" t="inlineStr">
+        <is>
+          <t>NodesPerMap</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>맵당 노드 수 (Depth 수)</t>
+        </is>
+      </c>
+      <c r="C11" s="21" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D11" s="21" t="inlineStr"/>
+      <c r="E11" s="21" t="inlineStr"/>
+      <c r="F11" s="21" t="inlineStr"/>
+      <c r="G11" s="21" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="22" t="inlineStr">
+        <is>
+          <t>MinBranches</t>
+        </is>
+      </c>
+      <c r="B12" s="22" t="inlineStr">
+        <is>
+          <t>레이어당 최소 분기</t>
+        </is>
+      </c>
+      <c r="C12" s="23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D12" s="23" t="inlineStr"/>
+      <c r="E12" s="23" t="inlineStr"/>
+      <c r="F12" s="23" t="inlineStr"/>
+      <c r="G12" s="23" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="20" t="inlineStr">
+        <is>
+          <t>MaxBranches</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>레이어당 최대 분기</t>
+        </is>
+      </c>
+      <c r="C13" s="21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D13" s="21" t="inlineStr"/>
+      <c r="E13" s="21" t="inlineStr"/>
+      <c r="F13" s="21" t="inlineStr"/>
+      <c r="G13" s="21" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="22" t="inlineStr">
+        <is>
+          <t>Depth 1</t>
+        </is>
+      </c>
+      <c r="B14" s="22" t="inlineStr">
+        <is>
+          <t>시작 노드 (항상 1개)</t>
+        </is>
+      </c>
+      <c r="C14" s="23" t="inlineStr">
+        <is>
+          <t>고정</t>
+        </is>
+      </c>
+      <c r="D14" s="23" t="inlineStr"/>
+      <c r="E14" s="23" t="inlineStr"/>
+      <c r="F14" s="23" t="inlineStr"/>
+      <c r="G14" s="23" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="20" t="inlineStr">
+        <is>
+          <t>Depth 50</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
+        <is>
+          <t>보스 노드 (항상 1개)</t>
+        </is>
+      </c>
+      <c r="C15" s="21" t="inlineStr">
+        <is>
+          <t>고정</t>
+        </is>
+      </c>
+      <c r="D15" s="21" t="inlineStr"/>
+      <c r="E15" s="21" t="inlineStr"/>
+      <c r="F15" s="21" t="inlineStr"/>
+      <c r="G15" s="21" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="24" t="inlineStr">
+        <is>
+          <t>※ 가중치는 MapGenerationConfig.NodeWeights 리스트에서 관리. Boss는 항상 고정이므로 가중치 없음.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="24" t="inlineStr">
+        <is>
+          <t>※ 모든 경로는 Boss(Depth50)에서 합류. 막힌 경로(Dead End) 없음.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="24" t="inlineStr">
+        <is>
+          <t>※ UI: UI_Panel_MapPopup Prefab (Addressable). 노드 = Map_Node, 연결선 = Map_Line Prefab.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="24" t="inlineStr">
+        <is>
+          <t>※ Addressable Key: Map_GenerationConfig (MapGenerationConfig), Map_NodeIconData (NodeIconData).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A17:G17"/>
+    <mergeCell ref="A18:G18"/>
+    <mergeCell ref="A20:G20"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A19:G19"/>
+    <mergeCell ref="A10:G10"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/GameData/DataSheet.xlsx
+++ b/GameData/DataSheet.xlsx
@@ -4519,7 +4519,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="12.75"/>
   <cols>
     <col width="18" customWidth="1" style="21" min="1" max="1"/>
@@ -4900,17 +4900,17 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Item_Key</t>
+          <t>Item_Potion_Medium</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>열쇠</t>
+          <t>회복약(중)</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Chest Key</t>
+          <t>Health Potion (Medium)</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
@@ -4920,34 +4920,34 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t>Common</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+10 HP</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>잠긴 보물상자 개방에 사용 (현재 미구현)</t>
+          <t>인벤토리에서 사용 시 체력 10 회복</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Item_Chest</t>
+          <t>Item_Potion_Large</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>보물상자</t>
+          <t>회복약(대)</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Treasure Box</t>
+          <t>Health Potion (Large)</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
@@ -4957,54 +4957,202 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>Epic</t>
+          <t>Common</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+20 HP</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>사용 시 랜덤 보상 획득</t>
+          <t>인벤토리에서 사용 시 체력 20 회복</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
+          <t>Item_Key</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>열쇠</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>Chest Key</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>Consumable</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>잠긴 보물상자 개방에 사용 (현재 미구현)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Item_Chest</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>보물상자</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Treasure Box</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>Consumable</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>사용 시 랜덤 보상 획득</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
           <t>Item_Special</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>특수 소모품</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>Elixir</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>Consumable</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr">
+      <c r="E17" s="5" t="inlineStr">
         <is>
           <t>Legendary</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="F17" s="5" t="inlineStr">
         <is>
           <t>+10 HP</t>
         </is>
       </c>
-      <c r="G15" s="4" t="inlineStr">
+      <c r="G17" s="4" t="inlineStr">
         <is>
           <t>사용 시 체력 10 회복</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Item_PortableAnvil</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>간이 모루</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>Portable Anvil</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>Consumable</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>+5 내구도</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>인벤토리에서 사용 시 곡괭이 내구도 5 회복 (최대치 초과 불가)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Item_ImmortalityPotion</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>불사 물약</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>Potion of Immortality</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>Consumable</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>Legendary</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>사망 시 자동 소비되어 체력 5로 부활 (1회 한정, 수동 사용 불가)</t>
         </is>
       </c>
     </row>

--- a/GameData/DataSheet.xlsx
+++ b/GameData/DataSheet.xlsx
@@ -4519,7 +4519,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="12.75"/>
   <cols>
     <col width="18" customWidth="1" style="21" min="1" max="1"/>
@@ -5153,6 +5153,339 @@
       <c r="G19" s="4" t="inlineStr">
         <is>
           <t>사망 시 자동 소비되어 체력 5로 부활 (1회 한정, 수동 사용 불가)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Item_RepairKit</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>수리 키트</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Repair Kit</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Consumable</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>+3 내구도</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>인벤토리에서 사용 시 곡괭이 내구도 3 회복</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Item_AntidotePotion</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>해독제</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Antidote</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Consumable</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>인벤토리에서 사용 시 중독 상태 즉시 해제</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Item_Bomb</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>폭탄</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Bomb</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Consumable</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>5 피해</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>전투 중인 몬스터 전체에게 5의 피해. 전투 중에만 사용 가능</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Item_HolyWater</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>정화의 성수</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Holy Water</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Consumable</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>인벤토리에서 사용 시 화상+중독 상태 동시 해제</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Item_EnhancedRepairKit</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>강화 수리 키트</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Enhanced Repair Kit</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Consumable</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>+10 내구도</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>인벤토리에서 사용 시 곡괭이 내구도 10 회복</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Item_EnhancedBomb</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>강화 폭탄</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Enhanced Bomb</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Consumable</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>15 피해</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>전투 중인 몬스터 전체에게 15의 피해. 전투 중에만 사용 가능</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Item_AngelFeather</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>천사의 깃털</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Angel Feather</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Consumable</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Legendary</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>풀 HP 회복</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>체력 완전 회복 + 화상/중독 동시 치료</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Item_FullRepairKit</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>완전 수리 키트</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Full Repair Kit</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Consumable</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Legendary</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>풀 내구도</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>곡괭이 내구도 완전 회복</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Item_GuardianHeart</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>수호자의 심장</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Guardian's Heart</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Consumable</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Legendary</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>사망 시 자동 소비되어 체력 15로 부활 (1회 한정, 수동 사용 불가)</t>
         </is>
       </c>
     </row>

--- a/GameData/DataSheet.xlsx
+++ b/GameData/DataSheet.xlsx
@@ -1058,7 +1058,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N68"/>
+  <dimension ref="A1:N120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="12.75"/>
   <cols>
     <col width="26" customWidth="1" style="21" min="1" max="1"/>
@@ -4505,6 +4505,2814 @@
       <c r="N68" s="4" t="inlineStr">
         <is>
           <t>엘리트 보상 2배  유물 추가</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="inlineStr">
+        <is>
+          <t>relic_stone_blessing</t>
+        </is>
+      </c>
+      <c r="B69" s="4" t="inlineStr">
+        <is>
+          <t>바위의 축복</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="inlineStr">
+        <is>
+          <t>Stone's Blessing</t>
+        </is>
+      </c>
+      <c r="D69" s="5" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="E69" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F69" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G69" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I69" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J69" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K69" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L69" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M69" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N69" s="4" t="inlineStr">
+        <is>
+          <t>채굴 완료 시 10% 확률로 같은 광물 +1개 획득</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="inlineStr">
+        <is>
+          <t>relic_miner_backpack</t>
+        </is>
+      </c>
+      <c r="B70" s="4" t="inlineStr">
+        <is>
+          <t>광부의 배낭</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="inlineStr">
+        <is>
+          <t>Miner's Backpack</t>
+        </is>
+      </c>
+      <c r="D70" s="5" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="E70" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F70" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G70" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H70" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I70" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J70" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K70" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L70" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M70" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N70" s="4" t="inlineStr">
+        <is>
+          <t>인벤토리 사이즈 +10</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="4" t="inlineStr">
+        <is>
+          <t>relic_mining_gloves</t>
+        </is>
+      </c>
+      <c r="B71" s="4" t="inlineStr">
+        <is>
+          <t>채굴 장갑</t>
+        </is>
+      </c>
+      <c r="C71" s="4" t="inlineStr">
+        <is>
+          <t>Mining Gloves</t>
+        </is>
+      </c>
+      <c r="D71" s="5" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="E71" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F71" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G71" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H71" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="I71" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J71" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K71" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L71" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M71" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N71" s="4" t="inlineStr">
+        <is>
+          <t>광물 획득량 +10%</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t>relic_war_medal</t>
+        </is>
+      </c>
+      <c r="B72" s="4" t="inlineStr">
+        <is>
+          <t>전쟁의 메달</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>War Medal</t>
+        </is>
+      </c>
+      <c r="D72" s="5" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="E72" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F72" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G72" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H72" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I72" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J72" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K72" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L72" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M72" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N72" s="4" t="inlineStr">
+        <is>
+          <t>공격력 +2</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="4" t="inlineStr">
+        <is>
+          <t>relic_reinforced_whetstone</t>
+        </is>
+      </c>
+      <c r="B73" s="4" t="inlineStr">
+        <is>
+          <t>강화 숫돌</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="inlineStr">
+        <is>
+          <t>Reinforced Whetstone</t>
+        </is>
+      </c>
+      <c r="D73" s="5" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="E73" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F73" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G73" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H73" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I73" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J73" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K73" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L73" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M73" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N73" s="4" t="inlineStr">
+        <is>
+          <t>곡괭이 내구도 최대치 +20</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="4" t="inlineStr">
+        <is>
+          <t>relic_nail_pouch</t>
+        </is>
+      </c>
+      <c r="B74" s="4" t="inlineStr">
+        <is>
+          <t>철못 주머니</t>
+        </is>
+      </c>
+      <c r="C74" s="4" t="inlineStr">
+        <is>
+          <t>Nail Pouch</t>
+        </is>
+      </c>
+      <c r="D74" s="5" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="E74" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F74" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G74" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H74" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I74" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J74" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K74" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L74" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M74" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N74" s="4" t="inlineStr">
+        <is>
+          <t>곡괭이 내구도 감소량 10% 감소</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="4" t="inlineStr">
+        <is>
+          <t>relic_alchemy_notebook</t>
+        </is>
+      </c>
+      <c r="B75" s="4" t="inlineStr">
+        <is>
+          <t>연금술 노트</t>
+        </is>
+      </c>
+      <c r="C75" s="4" t="inlineStr">
+        <is>
+          <t>Alchemy Notebook</t>
+        </is>
+      </c>
+      <c r="D75" s="5" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="E75" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F75" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G75" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H75" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I75" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J75" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K75" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L75" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M75" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N75" s="4" t="inlineStr">
+        <is>
+          <t>포션 효과 +20%</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="4" t="inlineStr">
+        <is>
+          <t>relic_healing_herb</t>
+        </is>
+      </c>
+      <c r="B76" s="4" t="inlineStr">
+        <is>
+          <t>회복 허브</t>
+        </is>
+      </c>
+      <c r="C76" s="4" t="inlineStr">
+        <is>
+          <t>Healing Herb</t>
+        </is>
+      </c>
+      <c r="D76" s="5" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="E76" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F76" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G76" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H76" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I76" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J76" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K76" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L76" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M76" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N76" s="4" t="inlineStr">
+        <is>
+          <t>전투 종료 시 체력회복 +2</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="4" t="inlineStr">
+        <is>
+          <t>relic_holy_symbol</t>
+        </is>
+      </c>
+      <c r="B77" s="4" t="inlineStr">
+        <is>
+          <t>신성한 상징</t>
+        </is>
+      </c>
+      <c r="C77" s="4" t="inlineStr">
+        <is>
+          <t>Holy Symbol</t>
+        </is>
+      </c>
+      <c r="D77" s="5" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="E77" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F77" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G77" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H77" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I77" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K77" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="L77" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M77" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N77" s="4" t="inlineStr">
+        <is>
+          <t>화상, 독 데미지 무효</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="4" t="inlineStr">
+        <is>
+          <t>relic_old_map</t>
+        </is>
+      </c>
+      <c r="B78" s="4" t="inlineStr">
+        <is>
+          <t>오래된 지도</t>
+        </is>
+      </c>
+      <c r="C78" s="4" t="inlineStr">
+        <is>
+          <t>Old Map</t>
+        </is>
+      </c>
+      <c r="D78" s="5" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="E78" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F78" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G78" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H78" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I78" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J78" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K78" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L78" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M78" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N78" s="4" t="inlineStr">
+        <is>
+          <t>이벤트 노드 도착 시 최대 체력 +1, 체력 3 회복</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="4" t="inlineStr">
+        <is>
+          <t>relic_explorers_journal</t>
+        </is>
+      </c>
+      <c r="B79" s="4" t="inlineStr">
+        <is>
+          <t>탐험가의 일지</t>
+        </is>
+      </c>
+      <c r="C79" s="4" t="inlineStr">
+        <is>
+          <t>Explorer's Journal</t>
+        </is>
+      </c>
+      <c r="D79" s="5" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="E79" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F79" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G79" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H79" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I79" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K79" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L79" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M79" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N79" s="4" t="inlineStr">
+        <is>
+          <t>이벤트 노드 도착 시 공격력 +2</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="4" t="inlineStr">
+        <is>
+          <t>relic_constellation_compass</t>
+        </is>
+      </c>
+      <c r="B80" s="4" t="inlineStr">
+        <is>
+          <t>별자리 나침반</t>
+        </is>
+      </c>
+      <c r="C80" s="4" t="inlineStr">
+        <is>
+          <t>Constellation Compass</t>
+        </is>
+      </c>
+      <c r="D80" s="5" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="E80" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F80" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G80" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H80" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I80" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J80" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K80" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L80" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M80" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N80" s="4" t="inlineStr">
+        <is>
+          <t>이벤트 노드 완료 시 채굴력 +2</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="4" t="inlineStr">
+        <is>
+          <t>relic_treasure_detector</t>
+        </is>
+      </c>
+      <c r="B81" s="4" t="inlineStr">
+        <is>
+          <t>보물 감지기</t>
+        </is>
+      </c>
+      <c r="C81" s="4" t="inlineStr">
+        <is>
+          <t>Treasure Detector</t>
+        </is>
+      </c>
+      <c r="D81" s="5" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="E81" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F81" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G81" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H81" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I81" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J81" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K81" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L81" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M81" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N81" s="4" t="inlineStr">
+        <is>
+          <t>보물상자 노드 도착 시 최대 체력 +1, 공격력 +1</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="4" t="inlineStr">
+        <is>
+          <t>relic_ancient_key</t>
+        </is>
+      </c>
+      <c r="B82" s="4" t="inlineStr">
+        <is>
+          <t>고대 열쇠</t>
+        </is>
+      </c>
+      <c r="C82" s="4" t="inlineStr">
+        <is>
+          <t>Ancient Key</t>
+        </is>
+      </c>
+      <c r="D82" s="5" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="E82" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F82" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G82" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H82" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I82" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J82" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K82" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L82" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M82" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N82" s="4" t="inlineStr">
+        <is>
+          <t>보물상자 노드 완료 시 무작위 포션 1개 획득</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="4" t="inlineStr">
+        <is>
+          <t>relic_lucky_compass</t>
+        </is>
+      </c>
+      <c r="B83" s="4" t="inlineStr">
+        <is>
+          <t>행운의 나침반</t>
+        </is>
+      </c>
+      <c r="C83" s="4" t="inlineStr">
+        <is>
+          <t>Lucky Compass</t>
+        </is>
+      </c>
+      <c r="D83" s="5" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="E83" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F83" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G83" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H83" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I83" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J83" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K83" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L83" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M83" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N83" s="4" t="inlineStr">
+        <is>
+          <t>맵에서 이벤트 노드 등장 확률 증가</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="4" t="inlineStr">
+        <is>
+          <t>relic_golden_compass</t>
+        </is>
+      </c>
+      <c r="B84" s="4" t="inlineStr">
+        <is>
+          <t>황금 나침반</t>
+        </is>
+      </c>
+      <c r="C84" s="4" t="inlineStr">
+        <is>
+          <t>Golden Compass</t>
+        </is>
+      </c>
+      <c r="D84" s="5" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="E84" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F84" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G84" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H84" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I84" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J84" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K84" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L84" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M84" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N84" s="4" t="inlineStr">
+        <is>
+          <t>맵에서 보물상자 노드 등장 확률 증가</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="4" t="inlineStr">
+        <is>
+          <t>relic_travelers_backpack</t>
+        </is>
+      </c>
+      <c r="B85" s="4" t="inlineStr">
+        <is>
+          <t>여행자의 배낭</t>
+        </is>
+      </c>
+      <c r="C85" s="4" t="inlineStr">
+        <is>
+          <t>Traveler's Backpack</t>
+        </is>
+      </c>
+      <c r="D85" s="5" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="E85" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F85" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G85" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H85" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I85" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J85" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K85" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L85" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M85" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N85" s="4" t="inlineStr">
+        <is>
+          <t>소비 아이템 사용 시 1턴간 공격력 +2 (최대 2중첩)</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="4" t="inlineStr">
+        <is>
+          <t>relic_golden_flask</t>
+        </is>
+      </c>
+      <c r="B86" s="4" t="inlineStr">
+        <is>
+          <t>황금 플라스크</t>
+        </is>
+      </c>
+      <c r="C86" s="4" t="inlineStr">
+        <is>
+          <t>Golden Flask</t>
+        </is>
+      </c>
+      <c r="D86" s="5" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="E86" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F86" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G86" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H86" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I86" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J86" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K86" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L86" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M86" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N86" s="4" t="inlineStr">
+        <is>
+          <t>포션 사용 시 1턴간 공격력 +3 (최대 3중첩)</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="4" t="inlineStr">
+        <is>
+          <t>relic_mysterious_serum</t>
+        </is>
+      </c>
+      <c r="B87" s="4" t="inlineStr">
+        <is>
+          <t>신비한 시약</t>
+        </is>
+      </c>
+      <c r="C87" s="4" t="inlineStr">
+        <is>
+          <t>Mysterious Serum</t>
+        </is>
+      </c>
+      <c r="D87" s="5" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="E87" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F87" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G87" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H87" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I87" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J87" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K87" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L87" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M87" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N87" s="4" t="inlineStr">
+        <is>
+          <t>소비 아이템 사용 시 체력 1 회복</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="4" t="inlineStr">
+        <is>
+          <t>relic_ring_of_blessing</t>
+        </is>
+      </c>
+      <c r="B88" s="4" t="inlineStr">
+        <is>
+          <t>축복의 반지</t>
+        </is>
+      </c>
+      <c r="C88" s="4" t="inlineStr">
+        <is>
+          <t>Ring of Blessing</t>
+        </is>
+      </c>
+      <c r="D88" s="5" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="E88" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F88" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G88" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H88" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I88" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J88" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K88" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L88" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M88" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N88" s="4" t="inlineStr">
+        <is>
+          <t>포션 사용 시 화상과 중독 제거</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="4" t="inlineStr">
+        <is>
+          <t>relic_emergency_kit</t>
+        </is>
+      </c>
+      <c r="B89" s="4" t="inlineStr">
+        <is>
+          <t>응급 키트</t>
+        </is>
+      </c>
+      <c r="C89" s="4" t="inlineStr">
+        <is>
+          <t>Emergency Kit</t>
+        </is>
+      </c>
+      <c r="D89" s="5" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="E89" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F89" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G89" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H89" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I89" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J89" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K89" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L89" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M89" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N89" s="4" t="inlineStr">
+        <is>
+          <t>체력이 30% 이하일 때 포션 회복량 2배</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="4" t="inlineStr">
+        <is>
+          <t>relic_battle_axe</t>
+        </is>
+      </c>
+      <c r="B90" s="4" t="inlineStr">
+        <is>
+          <t>전투 도끼</t>
+        </is>
+      </c>
+      <c r="C90" s="4" t="inlineStr">
+        <is>
+          <t>Battle Axe</t>
+        </is>
+      </c>
+      <c r="D90" s="5" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="E90" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F90" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G90" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H90" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I90" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J90" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K90" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L90" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M90" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N90" s="4" t="inlineStr">
+        <is>
+          <t>전투 중 첫 공격 피해 +30% (전투당 1회)</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="4" t="inlineStr">
+        <is>
+          <t>relic_battle_gauntlet</t>
+        </is>
+      </c>
+      <c r="B91" s="4" t="inlineStr">
+        <is>
+          <t>전투 장갑</t>
+        </is>
+      </c>
+      <c r="C91" s="4" t="inlineStr">
+        <is>
+          <t>Battle Gauntlet</t>
+        </is>
+      </c>
+      <c r="D91" s="5" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="E91" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F91" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G91" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H91" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I91" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J91" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K91" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L91" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M91" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N91" s="4" t="inlineStr">
+        <is>
+          <t>전투 중 경과한 턴마다 공격력 +1 누적</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="4" t="inlineStr">
+        <is>
+          <t>relic_steel_armor</t>
+        </is>
+      </c>
+      <c r="B92" s="4" t="inlineStr">
+        <is>
+          <t>강철 갑옷</t>
+        </is>
+      </c>
+      <c r="C92" s="4" t="inlineStr">
+        <is>
+          <t>Steel Armor</t>
+        </is>
+      </c>
+      <c r="D92" s="5" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="E92" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F92" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G92" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H92" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I92" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J92" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K92" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L92" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M92" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N92" s="4" t="inlineStr">
+        <is>
+          <t>전투 첫 턴에 방어도 +3</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="4" t="inlineStr">
+        <is>
+          <t>relic_battle_flag</t>
+        </is>
+      </c>
+      <c r="B93" s="4" t="inlineStr">
+        <is>
+          <t>전장의 깃발</t>
+        </is>
+      </c>
+      <c r="C93" s="4" t="inlineStr">
+        <is>
+          <t>Battle Flag</t>
+        </is>
+      </c>
+      <c r="D93" s="5" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="E93" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F93" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G93" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H93" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I93" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J93" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K93" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L93" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M93" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N93" s="4" t="inlineStr">
+        <is>
+          <t>조우 중인 몬스터 1마리당 공격력 +2</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="4" t="inlineStr">
+        <is>
+          <t>relic_bracelet_of_rage</t>
+        </is>
+      </c>
+      <c r="B94" s="4" t="inlineStr">
+        <is>
+          <t>분노의 팔찌</t>
+        </is>
+      </c>
+      <c r="C94" s="4" t="inlineStr">
+        <is>
+          <t>Bracelet of Rage</t>
+        </is>
+      </c>
+      <c r="D94" s="5" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="E94" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F94" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G94" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H94" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I94" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J94" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K94" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L94" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M94" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N94" s="4" t="inlineStr">
+        <is>
+          <t>전투 중 실제 체력 피해를 입을 때마다 공격력 +2 누적</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="4" t="inlineStr">
+        <is>
+          <t>relic_paladins_cloak</t>
+        </is>
+      </c>
+      <c r="B95" s="4" t="inlineStr">
+        <is>
+          <t>성기사의 망토</t>
+        </is>
+      </c>
+      <c r="C95" s="4" t="inlineStr">
+        <is>
+          <t>Paladin's Cloak</t>
+        </is>
+      </c>
+      <c r="D95" s="5" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="E95" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F95" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G95" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H95" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I95" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J95" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K95" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L95" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M95" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N95" s="4" t="inlineStr">
+        <is>
+          <t>전투 중 매 턴 시작 시 방어도 +5</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="4" t="inlineStr">
+        <is>
+          <t>relic_blood_necklace</t>
+        </is>
+      </c>
+      <c r="B96" s="4" t="inlineStr">
+        <is>
+          <t>피의 목걸이</t>
+        </is>
+      </c>
+      <c r="C96" s="4" t="inlineStr">
+        <is>
+          <t>Blood Necklace</t>
+        </is>
+      </c>
+      <c r="D96" s="5" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="E96" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F96" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G96" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J96" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K96" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L96" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M96" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N96" s="4" t="inlineStr">
+        <is>
+          <t>몬스터 처치 시 체력 1 회복</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="4" t="inlineStr">
+        <is>
+          <t>relic_blood_ring</t>
+        </is>
+      </c>
+      <c r="B97" s="4" t="inlineStr">
+        <is>
+          <t>핏빛 반지</t>
+        </is>
+      </c>
+      <c r="C97" s="4" t="inlineStr">
+        <is>
+          <t>Blood Ring</t>
+        </is>
+      </c>
+      <c r="D97" s="5" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="E97" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F97" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G97" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I97" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J97" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K97" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L97" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M97" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N97" s="4" t="inlineStr">
+        <is>
+          <t>몬스터에게 피해를 입힐 때마다 체력 1 회복</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="4" t="inlineStr">
+        <is>
+          <t>relic_hunters_medal</t>
+        </is>
+      </c>
+      <c r="B98" s="4" t="inlineStr">
+        <is>
+          <t>사냥꾼의 훈장</t>
+        </is>
+      </c>
+      <c r="C98" s="4" t="inlineStr">
+        <is>
+          <t>Hunter's Medal</t>
+        </is>
+      </c>
+      <c r="D98" s="5" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="E98" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F98" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G98" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I98" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J98" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K98" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L98" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M98" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N98" s="4" t="inlineStr">
+        <is>
+          <t>엘리트 몬스터 처치 시 포션 추가 드롭</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="4" t="inlineStr">
+        <is>
+          <t>relic_maintenance_kit</t>
+        </is>
+      </c>
+      <c r="B99" s="4" t="inlineStr">
+        <is>
+          <t>정비 키트</t>
+        </is>
+      </c>
+      <c r="C99" s="4" t="inlineStr">
+        <is>
+          <t>Maintenance Kit</t>
+        </is>
+      </c>
+      <c r="D99" s="5" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="E99" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F99" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G99" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H99" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I99" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J99" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K99" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L99" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M99" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N99" s="4" t="inlineStr">
+        <is>
+          <t>엘리트 또는 보스 처치 시 곡괭이 내구도 완전 회복</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="4" t="inlineStr">
+        <is>
+          <t>relic_alloy_handle</t>
+        </is>
+      </c>
+      <c r="B100" s="4" t="inlineStr">
+        <is>
+          <t>합금 손잡이</t>
+        </is>
+      </c>
+      <c r="C100" s="4" t="inlineStr">
+        <is>
+          <t>Alloy Handle</t>
+        </is>
+      </c>
+      <c r="D100" s="5" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="E100" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F100" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G100" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H100" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I100" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J100" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K100" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L100" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M100" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N100" s="4" t="inlineStr">
+        <is>
+          <t>곡괭이 수리 시 체력 2 회복</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="4" t="inlineStr">
+        <is>
+          <t>relic_furnace_core</t>
+        </is>
+      </c>
+      <c r="B101" s="4" t="inlineStr">
+        <is>
+          <t>용광로 코어</t>
+        </is>
+      </c>
+      <c r="C101" s="4" t="inlineStr">
+        <is>
+          <t>Furnace Core</t>
+        </is>
+      </c>
+      <c r="D101" s="5" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="E101" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F101" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G101" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H101" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I101" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J101" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K101" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L101" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M101" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N101" s="4" t="inlineStr">
+        <is>
+          <t>곡괭이 수리 시 10% 확률로 최대 내구도 영구 +1</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="4" t="inlineStr">
+        <is>
+          <t>relic_steel_hammer</t>
+        </is>
+      </c>
+      <c r="B102" s="4" t="inlineStr">
+        <is>
+          <t>강철 망치</t>
+        </is>
+      </c>
+      <c r="C102" s="4" t="inlineStr">
+        <is>
+          <t>Steel Hammer</t>
+        </is>
+      </c>
+      <c r="D102" s="5" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="E102" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F102" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G102" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H102" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I102" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J102" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K102" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L102" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M102" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N102" s="4" t="inlineStr">
+        <is>
+          <t>곡괭이 수리 효율 +50%</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="4" t="inlineStr">
+        <is>
+          <t>relic_reinforced_pickaxe_handle</t>
+        </is>
+      </c>
+      <c r="B103" s="4" t="inlineStr">
+        <is>
+          <t>강화 곡괭이 손잡이</t>
+        </is>
+      </c>
+      <c r="C103" s="4" t="inlineStr">
+        <is>
+          <t>Reinforced Pickaxe Handle</t>
+        </is>
+      </c>
+      <c r="D103" s="5" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="E103" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F103" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G103" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H103" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I103" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J103" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K103" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L103" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M103" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N103" s="4" t="inlineStr">
+        <is>
+          <t>보유 광물 9개당 채굴력 +1</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="4" t="inlineStr">
+        <is>
+          <t>relic_pickaxe_sword</t>
+        </is>
+      </c>
+      <c r="B104" s="4" t="inlineStr">
+        <is>
+          <t>곡괭이 검</t>
+        </is>
+      </c>
+      <c r="C104" s="4" t="inlineStr">
+        <is>
+          <t>Pickaxe Sword</t>
+        </is>
+      </c>
+      <c r="D104" s="5" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="E104" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F104" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G104" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H104" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I104" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J104" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K104" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L104" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M104" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N104" s="4" t="inlineStr">
+        <is>
+          <t>채굴력 3당 공격력 +1</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="4" t="inlineStr">
+        <is>
+          <t>relic_deep_breath</t>
+        </is>
+      </c>
+      <c r="B105" s="4" t="inlineStr">
+        <is>
+          <t>깊은 숨결</t>
+        </is>
+      </c>
+      <c r="C105" s="4" t="inlineStr">
+        <is>
+          <t>Deep Breath</t>
+        </is>
+      </c>
+      <c r="D105" s="5" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="E105" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F105" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G105" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H105" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I105" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J105" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K105" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L105" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M105" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N105" s="4" t="inlineStr">
+        <is>
+          <t>깊이 50m당 채굴력 +2</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="4" t="inlineStr">
+        <is>
+          <t>relic_whetstone_blade</t>
+        </is>
+      </c>
+      <c r="B106" s="4" t="inlineStr">
+        <is>
+          <t>숫돌 칼날</t>
+        </is>
+      </c>
+      <c r="C106" s="4" t="inlineStr">
+        <is>
+          <t>Whetstone Blade</t>
+        </is>
+      </c>
+      <c r="D106" s="5" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="E106" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F106" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G106" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H106" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I106" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J106" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K106" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L106" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M106" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N106" s="4" t="inlineStr">
+        <is>
+          <t>곡괭이 내구도에 비례해 공격력 증가</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="4" t="inlineStr">
+        <is>
+          <t>relic_berserkers_axe</t>
+        </is>
+      </c>
+      <c r="B107" s="4" t="inlineStr">
+        <is>
+          <t>광전사의 도끼</t>
+        </is>
+      </c>
+      <c r="C107" s="4" t="inlineStr">
+        <is>
+          <t>Berserker's Axe</t>
+        </is>
+      </c>
+      <c r="D107" s="5" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="E107" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F107" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G107" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H107" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I107" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J107" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K107" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L107" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M107" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N107" s="4" t="inlineStr">
+        <is>
+          <t>잃은 체력 10%당 공격력 +1</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="4" t="inlineStr">
+        <is>
+          <t>relic_blood_pact</t>
+        </is>
+      </c>
+      <c r="B108" s="4" t="inlineStr">
+        <is>
+          <t>피의 계약</t>
+        </is>
+      </c>
+      <c r="C108" s="4" t="inlineStr">
+        <is>
+          <t>Blood Pact</t>
+        </is>
+      </c>
+      <c r="D108" s="5" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="E108" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F108" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G108" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H108" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I108" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J108" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K108" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L108" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M108" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N108" s="4" t="inlineStr">
+        <is>
+          <t>체력 50% 이하일 때 피해 +10%</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="4" t="inlineStr">
+        <is>
+          <t>relic_red_heart</t>
+        </is>
+      </c>
+      <c r="B109" s="4" t="inlineStr">
+        <is>
+          <t>붉은 심장</t>
+        </is>
+      </c>
+      <c r="C109" s="4" t="inlineStr">
+        <is>
+          <t>Red Heart</t>
+        </is>
+      </c>
+      <c r="D109" s="5" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="E109" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F109" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G109" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H109" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I109" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J109" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K109" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L109" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M109" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N109" s="4" t="inlineStr">
+        <is>
+          <t>체력 30% 이하일 때 피해 +20%</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="4" t="inlineStr">
+        <is>
+          <t>relic_distillation_device</t>
+        </is>
+      </c>
+      <c r="B110" s="4" t="inlineStr">
+        <is>
+          <t>증류 장치</t>
+        </is>
+      </c>
+      <c r="C110" s="4" t="inlineStr">
+        <is>
+          <t>Distillation Device</t>
+        </is>
+      </c>
+      <c r="D110" s="5" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="E110" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F110" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G110" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H110" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I110" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J110" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K110" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L110" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M110" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N110" s="4" t="inlineStr">
+        <is>
+          <t>상점의 포션 가격이 뿌리 2개만큼 저렴해짐</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="4" t="inlineStr">
+        <is>
+          <t>relic_golden_ticket</t>
+        </is>
+      </c>
+      <c r="B111" s="4" t="inlineStr">
+        <is>
+          <t>황금 티켓</t>
+        </is>
+      </c>
+      <c r="C111" s="4" t="inlineStr">
+        <is>
+          <t>Golden Ticket</t>
+        </is>
+      </c>
+      <c r="D111" s="5" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="E111" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F111" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G111" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H111" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I111" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J111" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K111" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L111" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M111" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N111" s="4" t="inlineStr">
+        <is>
+          <t>상점의 모든 가격 -15%</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="4" t="inlineStr">
+        <is>
+          <t>relic_holy_water_bottle</t>
+        </is>
+      </c>
+      <c r="B112" s="4" t="inlineStr">
+        <is>
+          <t>성수병</t>
+        </is>
+      </c>
+      <c r="C112" s="4" t="inlineStr">
+        <is>
+          <t>Holy Water Bottle</t>
+        </is>
+      </c>
+      <c r="D112" s="5" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="E112" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F112" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G112" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H112" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I112" s="5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J112" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K112" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L112" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M112" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N112" s="4" t="inlineStr">
+        <is>
+          <t>화상, 중독 지속시간 -1턴</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="4" t="inlineStr">
+        <is>
+          <t>relic_blessed_shield</t>
+        </is>
+      </c>
+      <c r="B113" s="4" t="inlineStr">
+        <is>
+          <t>축복의 방패</t>
+        </is>
+      </c>
+      <c r="C113" s="4" t="inlineStr">
+        <is>
+          <t>Blessed Shield</t>
+        </is>
+      </c>
+      <c r="D113" s="5" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="E113" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F113" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G113" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H113" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I113" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J113" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K113" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L113" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M113" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N113" s="4" t="inlineStr">
+        <is>
+          <t>상태이상으로 받는 피해 -10%</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="4" t="inlineStr">
+        <is>
+          <t>relic_chalice_of_purification</t>
+        </is>
+      </c>
+      <c r="B114" s="4" t="inlineStr">
+        <is>
+          <t>정화의 성배</t>
+        </is>
+      </c>
+      <c r="C114" s="4" t="inlineStr">
+        <is>
+          <t>Chalice of Purification</t>
+        </is>
+      </c>
+      <c r="D114" s="5" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="E114" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F114" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G114" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H114" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I114" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J114" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K114" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L114" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M114" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N114" s="4" t="inlineStr">
+        <is>
+          <t>전투 종료 시 모든 디버프 제거</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="4" t="inlineStr">
+        <is>
+          <t>relic_ring_of_luck</t>
+        </is>
+      </c>
+      <c r="B115" s="4" t="inlineStr">
+        <is>
+          <t>행운의 반지</t>
+        </is>
+      </c>
+      <c r="C115" s="4" t="inlineStr">
+        <is>
+          <t>Ring of Luck</t>
+        </is>
+      </c>
+      <c r="D115" s="5" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="E115" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F115" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G115" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H115" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I115" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J115" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K115" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L115" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M115" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N115" s="4" t="inlineStr">
+        <is>
+          <t>Rare 이상 유물 등장 확률 +10%</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="4" t="inlineStr">
+        <is>
+          <t>relic_mysterious_key</t>
+        </is>
+      </c>
+      <c r="B116" s="4" t="inlineStr">
+        <is>
+          <t>신비한 열쇠</t>
+        </is>
+      </c>
+      <c r="C116" s="4" t="inlineStr">
+        <is>
+          <t>Mysterious Key</t>
+        </is>
+      </c>
+      <c r="D116" s="5" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="E116" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F116" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G116" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H116" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I116" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J116" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K116" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L116" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M116" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N116" s="4" t="inlineStr">
+        <is>
+          <t>보물상자에서 Rare 유물이 나올 가중치 증가</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="4" t="inlineStr">
+        <is>
+          <t>relic_golden_prayer_book</t>
+        </is>
+      </c>
+      <c r="B117" s="4" t="inlineStr">
+        <is>
+          <t>황금의 기도서</t>
+        </is>
+      </c>
+      <c r="C117" s="4" t="inlineStr">
+        <is>
+          <t>Golden Prayer Book</t>
+        </is>
+      </c>
+      <c r="D117" s="5" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="E117" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F117" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G117" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H117" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I117" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J117" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K117" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L117" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M117" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N117" s="4" t="inlineStr">
+        <is>
+          <t>이번 전투에서 상태이상으로 입은 피해량만큼 공격력 증가</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="4" t="inlineStr">
+        <is>
+          <t>relic_collectors_bag</t>
+        </is>
+      </c>
+      <c r="B118" s="4" t="inlineStr">
+        <is>
+          <t>수집가의 가방</t>
+        </is>
+      </c>
+      <c r="C118" s="4" t="inlineStr">
+        <is>
+          <t>Collector's Bag</t>
+        </is>
+      </c>
+      <c r="D118" s="5" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="E118" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F118" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G118" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H118" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I118" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J118" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K118" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L118" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M118" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N118" s="4" t="inlineStr">
+        <is>
+          <t>획득 즉시 보유 중인 다른 유물 1개의 효과를 복사한다</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="4" t="inlineStr">
+        <is>
+          <t>relic_grave_robbers_gloves</t>
+        </is>
+      </c>
+      <c r="B119" s="4" t="inlineStr">
+        <is>
+          <t>도굴꾼 장갑</t>
+        </is>
+      </c>
+      <c r="C119" s="4" t="inlineStr">
+        <is>
+          <t>Grave Robber's Gloves</t>
+        </is>
+      </c>
+      <c r="D119" s="5" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="E119" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F119" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G119" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H119" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I119" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J119" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K119" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L119" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M119" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N119" s="4" t="inlineStr">
+        <is>
+          <t>보물상자의 보상 선택지가 1개 늘어난다</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="4" t="inlineStr">
+        <is>
+          <t>relic_finishing_blow</t>
+        </is>
+      </c>
+      <c r="B120" s="4" t="inlineStr">
+        <is>
+          <t>최후의 일격</t>
+        </is>
+      </c>
+      <c r="C120" s="4" t="inlineStr">
+        <is>
+          <t>Finishing Blow</t>
+        </is>
+      </c>
+      <c r="D120" s="5" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="E120" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F120" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G120" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H120" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I120" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J120" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K120" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L120" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M120" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N120" s="4" t="inlineStr">
+        <is>
+          <t>상대의 체력 비율이 내 체력 비율보다 낮을 때 피해 2배 (전투당 1회)</t>
         </is>
       </c>
     </row>

--- a/GameData/DataSheet.xlsx
+++ b/GameData/DataSheet.xlsx
@@ -23,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Arial"/>
       <color rgb="FF000000"/>
@@ -70,6 +70,10 @@
       <family val="3"/>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -104,7 +108,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -186,11 +190,17 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -257,6 +267,10 @@
     <xf numFmtId="0" fontId="7" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -535,7 +549,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="18" customWidth="1" style="21" min="1" max="1"/>
@@ -544,6 +558,7 @@
     <col width="12" customWidth="1" style="21" min="4" max="4"/>
     <col width="14" customWidth="1" style="21" min="5" max="5"/>
     <col width="36" customWidth="1" style="21" min="6" max="6"/>
+    <col width="40" customWidth="1" style="21" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="18" customHeight="1" s="21">
@@ -577,18 +592,24 @@
           <t>설명</t>
         </is>
       </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="12.75" customHeight="1" s="21">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="28" t="inlineStr">
         <is>
           <t>[메타 재화]</t>
         </is>
       </c>
-      <c r="B2" s="3" t="n"/>
-      <c r="C2" s="3" t="n"/>
-      <c r="D2" s="3" t="n"/>
-      <c r="E2" s="3" t="n"/>
-      <c r="F2" s="3" t="n"/>
+      <c r="B2" s="28" t="n"/>
+      <c r="C2" s="28" t="n"/>
+      <c r="D2" s="28" t="n"/>
+      <c r="E2" s="28" t="n"/>
+      <c r="F2" s="28" t="n"/>
+      <c r="G2" s="28" t="inlineStr"/>
     </row>
     <row r="3" ht="12.75" customHeight="1" s="21">
       <c r="A3" s="4" t="inlineStr">
@@ -618,434 +639,54 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>런 종료 시 획득. 메타 업그레이드에 사용</t>
+          <t>런 종료 시 채굴한 광물 환산 + 깊이 보너스로 획득. 메타 업그레이드/캐릭터·곡괭이 해금에 사용</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>게임 내 유일한 메타 재화(MetaProgressionManager.Will). 과거 있던 "골드" 메타 재화 항목은 대응 시스템이 없어 삭제함</t>
         </is>
       </c>
     </row>
     <row r="4" ht="12.75" customHeight="1" s="21">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>골드</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>메타 재화</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>상점에서 아이템/곡괭이 구매에 사용</t>
-        </is>
-      </c>
+      <c r="A4" s="4" t="n"/>
+      <c r="B4" s="4" t="n"/>
+      <c r="C4" s="4" t="n"/>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="5" t="n"/>
+      <c r="F4" s="4" t="n"/>
     </row>
     <row r="5" ht="12.75" customHeight="1" s="21">
-      <c r="A5" s="6" t="n"/>
-      <c r="B5" s="6" t="n"/>
-      <c r="C5" s="6" t="n"/>
-      <c r="D5" s="6" t="n"/>
-      <c r="E5" s="6" t="n"/>
-      <c r="F5" s="6" t="n"/>
-    </row>
-    <row r="6" ht="12.75" customHeight="1" s="21">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>[자원]</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="n"/>
-      <c r="C6" s="3" t="n"/>
-      <c r="D6" s="3" t="n"/>
-      <c r="E6" s="3" t="n"/>
-      <c r="F6" s="3" t="n"/>
-    </row>
-    <row r="7" ht="12.75" customHeight="1" s="21">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>Item_Stone</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>돌</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>Stone</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>자원</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>Common</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>단단한 돌멩이. 채굴로 획득</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="12.75" customHeight="1" s="21">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>Item_Wood</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>나무</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>Wood</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>자원</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>Common</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>흔하게 볼 수 있는 나무 장작</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="12.75" customHeight="1" s="21">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>Item_Iron</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>철</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>Iron</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>자원</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>Common</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>철 광석. 장비 제작에 사용</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="12.75" customHeight="1" s="21">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>Item_Silver</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>은</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>Silver</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>자원</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>Rare</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>빛나는 은 광석</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="12.75" customHeight="1" s="21">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>Item_Gold</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>금</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>자원</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>Epic</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>번쩍이는 금 광석</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="12.75" customHeight="1" s="21">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>Item_Diamond</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>다이아</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>Diamond</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>자원</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>Legendary</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>눈부신 다이아몬드</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="12.75" customHeight="1" s="21">
-      <c r="A13" s="6" t="n"/>
-      <c r="B13" s="6" t="n"/>
-      <c r="C13" s="6" t="n"/>
-      <c r="D13" s="6" t="n"/>
-      <c r="E13" s="6" t="n"/>
-      <c r="F13" s="6" t="n"/>
-    </row>
-    <row r="14" ht="12.75" customHeight="1" s="21">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>[소모품]</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="n"/>
-      <c r="C14" s="3" t="n"/>
-      <c r="D14" s="3" t="n"/>
-      <c r="E14" s="3" t="n"/>
-      <c r="F14" s="3" t="n"/>
-    </row>
-    <row r="15" ht="12.75" customHeight="1" s="21">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>Item_Potion</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>회복약</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>Health Potion</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>소모품</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>Common</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>사용 시 체력 5 회복</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="12.75" customHeight="1" s="21">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>Item_BurnCure</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>화상 치료제</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>Burn Cure</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="inlineStr">
-        <is>
-          <t>소모품</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>Common</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>사용 시 화상 상태를 즉시 해제</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="12.75" customHeight="1" s="21">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>Item_Key</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>열쇠</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>Chest Key</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t>소모품</t>
-        </is>
-      </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>Rare</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>잠긴 상자를 열 수 있음</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="12.75" customHeight="1" s="21">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>Item_Chest</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>보물상자</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>Treasure Box</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="inlineStr">
-        <is>
-          <t>소모품</t>
-        </is>
-      </c>
-      <c r="E18" s="5" t="inlineStr">
-        <is>
-          <t>Epic</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>사용 시 랜덤 보상</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="12.75" customHeight="1" s="21">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>Item_Special</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>특수 소모품</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>Elixir</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="inlineStr">
-        <is>
-          <t>소모품</t>
-        </is>
-      </c>
-      <c r="E19" s="5" t="inlineStr">
-        <is>
-          <t>Legendary</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>사용 시 체력 10 회복</t>
-        </is>
-      </c>
-    </row>
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>※ 광석(철/은/금/다이아)·소모품은 재화가 아닌 인벤토리 아이템입니다. 상세 목록은 [아이템]/[광물] 시트를 참고하세요.</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="n"/>
+      <c r="C5" s="4" t="n"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="4" t="n"/>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>이전 버전에 있던 [자원]/[소모품] 하위 섹션은 [아이템] 시트와 중복되어 제거함</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="12.75" customHeight="1" s="21"/>
+    <row r="7" ht="12.75" customHeight="1" s="21"/>
+    <row r="8" ht="12.75" customHeight="1" s="21"/>
+    <row r="9" ht="12.75" customHeight="1" s="21"/>
+    <row r="10" ht="12.75" customHeight="1" s="21"/>
+    <row r="11" ht="12.75" customHeight="1" s="21"/>
+    <row r="12" ht="12.75" customHeight="1" s="21"/>
+    <row r="13" ht="12.75" customHeight="1" s="21"/>
+    <row r="14" ht="12.75" customHeight="1" s="21"/>
+    <row r="15" ht="12.75" customHeight="1" s="21"/>
+    <row r="16" ht="12.75" customHeight="1" s="21"/>
+    <row r="17" ht="12.75" customHeight="1" s="21"/>
+    <row r="18" ht="12.75" customHeight="1" s="21"/>
+    <row r="19" ht="12.75" customHeight="1" s="21"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="400" verticalDpi="400" copies="0"/>
@@ -1058,7 +699,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N120"/>
+  <dimension ref="A1:O132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="12.75"/>
   <cols>
     <col width="26" customWidth="1" style="21" min="1" max="1"/>
@@ -1066,6 +707,7 @@
     <col width="12" customWidth="1" style="21" min="4" max="4"/>
     <col width="10" customWidth="1" style="21" min="5" max="13"/>
     <col width="40" customWidth="1" style="21" min="14" max="14"/>
+    <col width="45" customWidth="1" style="21" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="18" customHeight="1" s="21">
@@ -1137,6 +779,11 @@
       <c r="N1" s="2" t="inlineStr">
         <is>
           <t>효과 요약</t>
+        </is>
+      </c>
+      <c r="O1" s="2" t="inlineStr">
+        <is>
+          <t>비고</t>
         </is>
       </c>
     </row>
@@ -1161,73 +808,73 @@
       <c r="N2" s="3" t="n"/>
     </row>
     <row r="3" ht="25.5" customHeight="1" s="21">
-      <c r="A3" s="18" t="inlineStr">
-        <is>
-          <t>HeatResistantCharm</t>
-        </is>
-      </c>
-      <c r="B3" s="18" t="inlineStr">
-        <is>
-          <t>내열 부적</t>
-        </is>
-      </c>
-      <c r="C3" s="18" t="inlineStr">
-        <is>
-          <t>Heat Resistant Charm</t>
-        </is>
-      </c>
-      <c r="D3" s="19" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>FrozenCrystal</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>냉동 수정</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>Frozen Crystal</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>Treasure</t>
         </is>
       </c>
-      <c r="E3" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" s="19" t="n">
-        <v>-3</v>
-      </c>
-      <c r="J3" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" s="18" t="inlineStr">
-        <is>
-          <t>화상 지속 -3턴</t>
+      <c r="E3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4" t="inlineStr">
+        <is>
+          <t>화상 피해 -1</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>FrozenCrystal</t>
+          <t>FirefighterHelmet</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>냉동 수정</t>
+          <t>소방관 헬멧</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Frozen Crystal</t>
+          <t>Firefighter Helmet</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
@@ -1248,7 +895,7 @@
         <v>0</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="J4" s="5" t="n">
         <v>-1</v>
@@ -1264,24 +911,24 @@
       </c>
       <c r="N4" s="4" t="inlineStr">
         <is>
-          <t>화상 피해 -1</t>
+          <t>화상 지속 -2턴, 피해 -1</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>FirefighterHelmet</t>
+          <t>PurificationRing</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>소방관 헬멧</t>
+          <t>정화의 반지</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Firefighter Helmet</t>
+          <t>Purification Ring</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
@@ -1302,13 +949,13 @@
         <v>0</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L5" s="5" t="n">
         <v>0</v>
@@ -1318,114 +965,114 @@
       </c>
       <c r="N5" s="4" t="inlineStr">
         <is>
-          <t>화상 지속 -2턴, 피해 -1</t>
+          <t>50% 확률로 화상 무효</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>PurificationRing</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>정화의 반지</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>Purification Ring</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="A6" s="6" t="n"/>
+      <c r="B6" s="6" t="n"/>
+      <c r="C6" s="6" t="n"/>
+      <c r="D6" s="6" t="n"/>
+      <c r="E6" s="6" t="n"/>
+      <c r="F6" s="6" t="n"/>
+      <c r="G6" s="6" t="n"/>
+      <c r="H6" s="6" t="n"/>
+      <c r="I6" s="6" t="n"/>
+      <c r="J6" s="6" t="n"/>
+      <c r="K6" s="6" t="n"/>
+      <c r="L6" s="6" t="n"/>
+      <c r="M6" s="6" t="n"/>
+      <c r="N6" s="6" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>[보물 유물 - 채굴 계열]</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n"/>
+      <c r="C7" s="3" t="n"/>
+      <c r="D7" s="3" t="n"/>
+      <c r="E7" s="3" t="n"/>
+      <c r="F7" s="3" t="n"/>
+      <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="n"/>
+      <c r="I7" s="3" t="n"/>
+      <c r="J7" s="3" t="n"/>
+      <c r="K7" s="3" t="n"/>
+      <c r="L7" s="3" t="n"/>
+      <c r="M7" s="3" t="n"/>
+      <c r="N7" s="3" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>relic_miners_gloves</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>광부의 장갑</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Miner's Gloves</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>Treasure</t>
         </is>
       </c>
-      <c r="E6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" s="5" t="n">
-        <v>50</v>
-      </c>
-      <c r="L6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" s="4" t="inlineStr">
-        <is>
-          <t>50% 확률로 화상 무효</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="n"/>
-      <c r="B7" s="6" t="n"/>
-      <c r="C7" s="6" t="n"/>
-      <c r="D7" s="6" t="n"/>
-      <c r="E7" s="6" t="n"/>
-      <c r="F7" s="6" t="n"/>
-      <c r="G7" s="6" t="n"/>
-      <c r="H7" s="6" t="n"/>
-      <c r="I7" s="6" t="n"/>
-      <c r="J7" s="6" t="n"/>
-      <c r="K7" s="6" t="n"/>
-      <c r="L7" s="6" t="n"/>
-      <c r="M7" s="6" t="n"/>
-      <c r="N7" s="6" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>[보물 유물 - 채굴 계열]</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="n"/>
-      <c r="C8" s="3" t="n"/>
-      <c r="D8" s="3" t="n"/>
-      <c r="E8" s="3" t="n"/>
-      <c r="F8" s="3" t="n"/>
-      <c r="G8" s="3" t="n"/>
-      <c r="H8" s="3" t="n"/>
-      <c r="I8" s="3" t="n"/>
-      <c r="J8" s="3" t="n"/>
-      <c r="K8" s="3" t="n"/>
-      <c r="L8" s="3" t="n"/>
-      <c r="M8" s="3" t="n"/>
-      <c r="N8" s="3" t="n"/>
+      <c r="E8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="4" t="inlineStr">
+        <is>
+          <t>채굴력 +1</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>relic_miners_gloves</t>
+          <t>relic_mining_king_helmet</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>광부의 장갑</t>
+          <t>채굴왕의 헬멧</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Miner's Gloves</t>
+          <t>Mining King's Helmet</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
@@ -1437,7 +1084,7 @@
         <v>0</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G9" s="5" t="n">
         <v>0</v>
@@ -1462,24 +1109,24 @@
       </c>
       <c r="N9" s="4" t="inlineStr">
         <is>
-          <t>채굴력 +1</t>
+          <t>채굴력 +2</t>
         </is>
       </c>
     </row>
     <row r="10" ht="25.5" customHeight="1" s="21">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>relic_mining_king_helmet</t>
+          <t>relic_broken_drill</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>채굴왕의 헬멧</t>
+          <t>부서진 드릴</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Mining King's Helmet</t>
+          <t>Broken Drill</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
@@ -1491,10 +1138,10 @@
         <v>0</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="H10" s="5" t="n">
         <v>0</v>
@@ -1516,24 +1163,24 @@
       </c>
       <c r="N10" s="4" t="inlineStr">
         <is>
-          <t>채굴력 +2</t>
+          <t>채굴력 +3, 최대체력 -5</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>relic_broken_drill</t>
+          <t>relic_ore_detector</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>부서진 드릴</t>
+          <t>광맥 탐지기</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Broken Drill</t>
+          <t>Ore Detector</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
@@ -1545,13 +1192,13 @@
         <v>0</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I11" s="5" t="n">
         <v>0</v>
@@ -1570,114 +1217,114 @@
       </c>
       <c r="N11" s="4" t="inlineStr">
         <is>
-          <t>채굴력 +3, 최대체력 -5</t>
+          <t>채굴력 +1, 광물 +20%</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>relic_ore_detector</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>광맥 탐지기</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>Ore Detector</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="A12" s="6" t="n"/>
+      <c r="B12" s="6" t="n"/>
+      <c r="C12" s="6" t="n"/>
+      <c r="D12" s="6" t="n"/>
+      <c r="E12" s="6" t="n"/>
+      <c r="F12" s="6" t="n"/>
+      <c r="G12" s="6" t="n"/>
+      <c r="H12" s="6" t="n"/>
+      <c r="I12" s="6" t="n"/>
+      <c r="J12" s="6" t="n"/>
+      <c r="K12" s="6" t="n"/>
+      <c r="L12" s="6" t="n"/>
+      <c r="M12" s="6" t="n"/>
+      <c r="N12" s="6" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>[보물 유물 - 전투 계열]</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n"/>
+      <c r="C13" s="3" t="n"/>
+      <c r="D13" s="3" t="n"/>
+      <c r="E13" s="3" t="n"/>
+      <c r="F13" s="3" t="n"/>
+      <c r="G13" s="3" t="n"/>
+      <c r="H13" s="3" t="n"/>
+      <c r="I13" s="3" t="n"/>
+      <c r="J13" s="3" t="n"/>
+      <c r="K13" s="3" t="n"/>
+      <c r="L13" s="3" t="n"/>
+      <c r="M13" s="3" t="n"/>
+      <c r="N13" s="3" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>relic_warriors_ring</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>전사의 반지</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Warrior's Ring</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>Treasure</t>
         </is>
       </c>
-      <c r="E12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" s="5" t="n">
+      <c r="E14" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="G12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" s="5" t="n">
-        <v>20</v>
-      </c>
-      <c r="I12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" s="4" t="inlineStr">
-        <is>
-          <t>채굴력 +1, 광물 +20%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="6" t="n"/>
-      <c r="B13" s="6" t="n"/>
-      <c r="C13" s="6" t="n"/>
-      <c r="D13" s="6" t="n"/>
-      <c r="E13" s="6" t="n"/>
-      <c r="F13" s="6" t="n"/>
-      <c r="G13" s="6" t="n"/>
-      <c r="H13" s="6" t="n"/>
-      <c r="I13" s="6" t="n"/>
-      <c r="J13" s="6" t="n"/>
-      <c r="K13" s="6" t="n"/>
-      <c r="L13" s="6" t="n"/>
-      <c r="M13" s="6" t="n"/>
-      <c r="N13" s="6" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>[보물 유물 - 전투 계열]</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="n"/>
-      <c r="C14" s="3" t="n"/>
-      <c r="D14" s="3" t="n"/>
-      <c r="E14" s="3" t="n"/>
-      <c r="F14" s="3" t="n"/>
-      <c r="G14" s="3" t="n"/>
-      <c r="H14" s="3" t="n"/>
-      <c r="I14" s="3" t="n"/>
-      <c r="J14" s="3" t="n"/>
-      <c r="K14" s="3" t="n"/>
-      <c r="L14" s="3" t="n"/>
-      <c r="M14" s="3" t="n"/>
-      <c r="N14" s="3" t="n"/>
+      <c r="F14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" s="4" t="inlineStr">
+        <is>
+          <t>공격력 +1</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>relic_warriors_ring</t>
+          <t>relic_mercenary_medal</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>전사의 반지</t>
+          <t>용병의 훈장</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Warrior's Ring</t>
+          <t>Mercenary's Medal</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
@@ -1686,7 +1333,7 @@
         </is>
       </c>
       <c r="E15" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F15" s="5" t="n">
         <v>0</v>
@@ -1714,24 +1361,24 @@
       </c>
       <c r="N15" s="4" t="inlineStr">
         <is>
-          <t>공격력 +1</t>
+          <t>공격력 +2</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>relic_mercenary_medal</t>
+          <t>relic_blood_contract</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>용병의 훈장</t>
+          <t>피의 계약서</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Mercenary's Medal</t>
+          <t>Blood Contract</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
@@ -1740,13 +1387,13 @@
         </is>
       </c>
       <c r="E16" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F16" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="H16" s="5" t="n">
         <v>0</v>
@@ -1768,24 +1415,24 @@
       </c>
       <c r="N16" s="4" t="inlineStr">
         <is>
-          <t>공격력 +2</t>
+          <t>공격력 +3, 최대체력 -5</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>relic_blood_contract</t>
+          <t>relic_hunters_eye</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>피의 계약서</t>
+          <t>사냥꾼의 눈</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Blood Contract</t>
+          <t>Hunter's Eye</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
@@ -1794,142 +1441,142 @@
         </is>
       </c>
       <c r="E17" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" s="5" t="n">
+        <v>-2</v>
+      </c>
+      <c r="N17" s="4" t="inlineStr">
+        <is>
+          <t>공격력 +1, 곡괭이 내구도 -2</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="n"/>
+      <c r="B18" s="6" t="n"/>
+      <c r="C18" s="6" t="n"/>
+      <c r="D18" s="6" t="n"/>
+      <c r="E18" s="6" t="n"/>
+      <c r="F18" s="6" t="n"/>
+      <c r="G18" s="6" t="n"/>
+      <c r="H18" s="6" t="n"/>
+      <c r="I18" s="6" t="n"/>
+      <c r="J18" s="6" t="n"/>
+      <c r="K18" s="6" t="n"/>
+      <c r="L18" s="6" t="n"/>
+      <c r="M18" s="6" t="n"/>
+      <c r="N18" s="6" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>[무덤 저주 유물]</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n"/>
+      <c r="C19" s="3" t="n"/>
+      <c r="D19" s="3" t="n"/>
+      <c r="E19" s="3" t="n"/>
+      <c r="F19" s="3" t="n"/>
+      <c r="G19" s="3" t="n"/>
+      <c r="H19" s="3" t="n"/>
+      <c r="I19" s="3" t="n"/>
+      <c r="J19" s="3" t="n"/>
+      <c r="K19" s="3" t="n"/>
+      <c r="L19" s="3" t="n"/>
+      <c r="M19" s="3" t="n"/>
+      <c r="N19" s="3" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>BurningHeart</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>불타는 심장</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>Burning Heart</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>Tombstone</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="F17" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" s="5" t="n">
-        <v>-5</v>
-      </c>
-      <c r="H17" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" s="4" t="inlineStr">
-        <is>
-          <t>공격력 +3, 최대체력 -5</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>relic_hunters_eye</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>사냥꾼의 눈</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>Hunter's Eye</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="inlineStr">
-        <is>
-          <t>Treasure</t>
-        </is>
-      </c>
-      <c r="E18" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F18" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" s="5" t="n">
-        <v>-2</v>
-      </c>
-      <c r="N18" s="4" t="inlineStr">
-        <is>
-          <t>공격력 +1, 곡괭이 내구도 -2</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="6" t="n"/>
-      <c r="B19" s="6" t="n"/>
-      <c r="C19" s="6" t="n"/>
-      <c r="D19" s="6" t="n"/>
-      <c r="E19" s="6" t="n"/>
-      <c r="F19" s="6" t="n"/>
-      <c r="G19" s="6" t="n"/>
-      <c r="H19" s="6" t="n"/>
-      <c r="I19" s="6" t="n"/>
-      <c r="J19" s="6" t="n"/>
-      <c r="K19" s="6" t="n"/>
-      <c r="L19" s="6" t="n"/>
-      <c r="M19" s="6" t="n"/>
-      <c r="N19" s="6" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>[무덤 저주 유물]</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="n"/>
-      <c r="C20" s="3" t="n"/>
-      <c r="D20" s="3" t="n"/>
-      <c r="E20" s="3" t="n"/>
-      <c r="F20" s="3" t="n"/>
-      <c r="G20" s="3" t="n"/>
-      <c r="H20" s="3" t="n"/>
-      <c r="I20" s="3" t="n"/>
-      <c r="J20" s="3" t="n"/>
-      <c r="K20" s="3" t="n"/>
-      <c r="L20" s="3" t="n"/>
-      <c r="M20" s="3" t="n"/>
-      <c r="N20" s="3" t="n"/>
+      <c r="J20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" s="4" t="inlineStr">
+        <is>
+          <t>공격력 +2, 화상 지속 +3턴</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>BurningHeart</t>
+          <t>LavaContract</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>불타는 심장</t>
+          <t>용암 계약</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Burning Heart</t>
+          <t>Lava Contract</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
@@ -1938,7 +1585,7 @@
         </is>
       </c>
       <c r="E21" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F21" s="5" t="n">
         <v>0</v>
@@ -1947,13 +1594,13 @@
         <v>0</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="I21" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" s="5" t="n">
         <v>0</v>
@@ -1966,24 +1613,24 @@
       </c>
       <c r="N21" s="4" t="inlineStr">
         <is>
-          <t>공격력 +2, 화상 지속 +3턴</t>
+          <t>광물 +25%, 화상 피해 +1</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>LavaContract</t>
+          <t>CursedAsh</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>용암 계약</t>
+          <t>저주받은 재</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>Lava Contract</t>
+          <t>Cursed Ash</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
@@ -1998,16 +1645,16 @@
         <v>0</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H22" s="5" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J22" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K22" s="5" t="n">
         <v>0</v>
@@ -2020,24 +1667,24 @@
       </c>
       <c r="N22" s="4" t="inlineStr">
         <is>
-          <t>광물 +25%, 화상 피해 +1</t>
+          <t>최대체력 +5, 화상 지속 +5턴</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>CursedAsh</t>
+          <t>FireCultMask</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>저주받은 재</t>
+          <t>불의 교단 가면</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Cursed Ash</t>
+          <t>Fire Cult Mask</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
@@ -2052,46 +1699,46 @@
         <v>0</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H23" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I23" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J23" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K23" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L23" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M23" s="5" t="n">
         <v>0</v>
       </c>
       <c r="N23" s="4" t="inlineStr">
         <is>
-          <t>최대체력 +5, 화상 지속 +5턴</t>
+          <t>몬스터 공격 +2, 화상 피해 +2</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>FireCultMask</t>
+          <t>relic_cursed_pickaxe</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>불의 교단 가면</t>
+          <t>저주받은 곡괭이</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>Fire Cult Mask</t>
+          <t>Cursed Pickaxe</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
@@ -2103,7 +1750,7 @@
         <v>0</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G24" s="5" t="n">
         <v>0</v>
@@ -2115,37 +1762,37 @@
         <v>0</v>
       </c>
       <c r="J24" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K24" s="5" t="n">
         <v>0</v>
       </c>
       <c r="L24" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M24" s="5" t="n">
         <v>0</v>
       </c>
       <c r="N24" s="4" t="inlineStr">
         <is>
-          <t>몬스터 공격 +2, 화상 피해 +2</t>
+          <t>채굴력 +2, 화상 피해 +1</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>relic_cursed_pickaxe</t>
+          <t>relic_madness_sword</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>저주받은 곡괭이</t>
+          <t>광기의 검</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>Cursed Pickaxe</t>
+          <t>Blade of Madness</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
@@ -2154,10 +1801,10 @@
         </is>
       </c>
       <c r="E25" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G25" s="5" t="n">
         <v>0</v>
@@ -2169,7 +1816,7 @@
         <v>0</v>
       </c>
       <c r="J25" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K25" s="5" t="n">
         <v>0</v>
@@ -2178,28 +1825,28 @@
         <v>0</v>
       </c>
       <c r="M25" s="5" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="N25" s="4" t="inlineStr">
         <is>
-          <t>채굴력 +2, 화상 피해 +1</t>
+          <t>공격력 +2, 곡괭이 내구도 -3</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>relic_madness_sword</t>
+          <t>relic_cursed_mining_gloves</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>광기의 검</t>
+          <t>저주받은 채굴 장갑</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>Blade of Madness</t>
+          <t>Cursed Mining Gloves</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
@@ -2208,13 +1855,13 @@
         </is>
       </c>
       <c r="E26" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F26" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="H26" s="5" t="n">
         <v>0</v>
@@ -2232,28 +1879,28 @@
         <v>0</v>
       </c>
       <c r="M26" s="5" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="N26" s="4" t="inlineStr">
         <is>
-          <t>공격력 +2, 곡괭이 내구도 -3</t>
+          <t>채굴력 +1, 최대체력 -3</t>
         </is>
       </c>
     </row>
     <row r="27" ht="25.5" customHeight="1" s="21">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>relic_cursed_mining_gloves</t>
+          <t>relic_blood_rune</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>저주받은 채굴 장갑</t>
+          <t>피의 룬</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>Cursed Mining Gloves</t>
+          <t>Blood Rune</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
@@ -2262,19 +1909,19 @@
         </is>
       </c>
       <c r="E27" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F27" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="H27" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I27" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J27" s="5" t="n">
         <v>0</v>
@@ -2290,37 +1937,37 @@
       </c>
       <c r="N27" s="4" t="inlineStr">
         <is>
-          <t>채굴력 +1, 최대체력 -3</t>
+          <t>공격력 +1, 화상 지속 +2턴</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>relic_blood_rune</t>
+          <t>relic_miner_glove</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>피의 룬</t>
+          <t>광부의 장갑</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>Blood Rune</t>
+          <t>Miner's Glove</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>Tombstone</t>
+          <t>Common</t>
         </is>
       </c>
       <c r="E28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F28" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="G28" s="5" t="n">
         <v>0</v>
       </c>
@@ -2328,7 +1975,7 @@
         <v>0</v>
       </c>
       <c r="I28" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J28" s="5" t="n">
         <v>0</v>
@@ -2344,24 +1991,24 @@
       </c>
       <c r="N28" s="4" t="inlineStr">
         <is>
-          <t>공격력 +1, 화상 지속 +2턴</t>
+          <t>채굴력 +1</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>relic_miner_glove</t>
+          <t>relic_old_whetstone</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>광부의 장갑</t>
+          <t>낡은 숫돌</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Miner's Glove</t>
+          <t>Old Whetstone</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
@@ -2370,10 +2017,10 @@
         </is>
       </c>
       <c r="E29" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G29" s="5" t="n">
         <v>0</v>
@@ -2398,24 +2045,24 @@
       </c>
       <c r="N29" s="4" t="inlineStr">
         <is>
-          <t>채굴력 +1</t>
+          <t>공격력 +1</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>relic_old_whetstone</t>
+          <t>relic_sturdy_backpack</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>낡은 숫돌</t>
+          <t>튼튼한 배낭</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>Old Whetstone</t>
+          <t>Sturdy Backpack</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
@@ -2424,7 +2071,7 @@
         </is>
       </c>
       <c r="E30" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F30" s="5" t="n">
         <v>0</v>
@@ -2452,24 +2099,24 @@
       </c>
       <c r="N30" s="4" t="inlineStr">
         <is>
-          <t>공격력 +1</t>
+          <t>인벤토리 +5칸</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>relic_sturdy_backpack</t>
+          <t>relic_emergency_bandage</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>튼튼한 배낭</t>
+          <t>응급 붕대</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Sturdy Backpack</t>
+          <t>Emergency Bandage</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
@@ -2506,24 +2153,24 @@
       </c>
       <c r="N31" s="4" t="inlineStr">
         <is>
-          <t>인벤토리 +5칸</t>
+          <t>전투 후 HP +1</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>relic_emergency_bandage</t>
+          <t>relic_reinforced_handle</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>응급 붕대</t>
+          <t>보강 손잡이</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>Emergency Bandage</t>
+          <t>Reinforced Handle</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
@@ -2560,24 +2207,24 @@
       </c>
       <c r="N32" s="4" t="inlineStr">
         <is>
-          <t>전투 후 HP +1</t>
+          <t>최대 내구도 +10</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>relic_reinforced_handle</t>
+          <t>relic_oil_bottle</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>보강 손잡이</t>
+          <t>기름병</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Reinforced Handle</t>
+          <t>Oil Bottle</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
@@ -2614,24 +2261,24 @@
       </c>
       <c r="N33" s="4" t="inlineStr">
         <is>
-          <t>최대 내구도 +10</t>
+          <t>내구도 소모 -20%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>relic_oil_bottle</t>
+          <t>relic_iron_ornament</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>기름병</t>
+          <t>철 곡괭이 장식</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>Oil Bottle</t>
+          <t>Iron Pickaxe Ornament</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
@@ -2668,24 +2315,24 @@
       </c>
       <c r="N34" s="4" t="inlineStr">
         <is>
-          <t>내구도 소모 -20%</t>
+          <t>철 획득 +20%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>relic_iron_ornament</t>
+          <t>relic_silver_necklace</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>철 곡괭이 장식</t>
+          <t>은 목걸이</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>Iron Pickaxe Ornament</t>
+          <t>Silver Necklace</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
@@ -2722,24 +2369,24 @@
       </c>
       <c r="N35" s="4" t="inlineStr">
         <is>
-          <t>철 획득 +20%</t>
+          <t>은 획득 +20%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>relic_silver_necklace</t>
+          <t>relic_gold_pouch</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>은 목걸이</t>
+          <t>금 주머니</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>Silver Necklace</t>
+          <t>Gold Pouch</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
@@ -2776,24 +2423,24 @@
       </c>
       <c r="N36" s="4" t="inlineStr">
         <is>
-          <t>은 획득 +20%</t>
+          <t>금 획득 +20%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>relic_gold_pouch</t>
+          <t>relic_diamond_brooch</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>금 주머니</t>
+          <t>다이아 브로치</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>Gold Pouch</t>
+          <t>Diamond Brooch</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
@@ -2830,24 +2477,24 @@
       </c>
       <c r="N37" s="4" t="inlineStr">
         <is>
-          <t>금 획득 +20%</t>
+          <t>다이아 획득 +20%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>relic_diamond_brooch</t>
+          <t>relic_miner_canteen</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>다이아 브로치</t>
+          <t>광부의 물통</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>Diamond Brooch</t>
+          <t>Miner's Canteen</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
@@ -2868,7 +2515,7 @@
         <v>0</v>
       </c>
       <c r="I38" s="5" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="J38" s="5" t="n">
         <v>0</v>
@@ -2884,24 +2531,24 @@
       </c>
       <c r="N38" s="4" t="inlineStr">
         <is>
-          <t>다이아 획득 +20%</t>
+          <t>화상 지속 -2턴</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>relic_miner_canteen</t>
+          <t>relic_work_glove</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>광부의 물통</t>
+          <t>작업용 장갑</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>Miner's Canteen</t>
+          <t>Work Glove</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
@@ -2922,7 +2569,7 @@
         <v>0</v>
       </c>
       <c r="I39" s="5" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="J39" s="5" t="n">
         <v>0</v>
@@ -2938,24 +2585,24 @@
       </c>
       <c r="N39" s="4" t="inlineStr">
         <is>
-          <t>화상 지속 -2턴</t>
+          <t>내구도 50% 이상 시 채굴력 +1</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>relic_work_glove</t>
+          <t>relic_iron_boot</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>작업용 장갑</t>
+          <t>철못 장화</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>Work Glove</t>
+          <t>Iron-Nail Boot</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
@@ -2992,24 +2639,24 @@
       </c>
       <c r="N40" s="4" t="inlineStr">
         <is>
-          <t>내구도 50% 이상 시 채굴력 +1</t>
+          <t>함정 피해 -1</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>relic_iron_boot</t>
+          <t>relic_small_whetstone</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>철못 장화</t>
+          <t>작은 숫돌</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>Iron-Nail Boot</t>
+          <t>Small Whetstone</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
@@ -3046,24 +2693,24 @@
       </c>
       <c r="N41" s="4" t="inlineStr">
         <is>
-          <t>함정 피해 -1</t>
+          <t>엘리트 피해 +10%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>relic_small_whetstone</t>
+          <t>relic_lucky_pickaxe</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>작은 숫돌</t>
+          <t>행운의 곡괭이</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>Small Whetstone</t>
+          <t>Lucky Pickaxe</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
@@ -3100,24 +2747,24 @@
       </c>
       <c r="N42" s="4" t="inlineStr">
         <is>
-          <t>엘리트 피해 +10%</t>
+          <t>채굴 시 5% 추가 획득</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>relic_lucky_pickaxe</t>
+          <t>relic_miner_lunchbox</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>행운의 곡괭이</t>
+          <t>광산 도시락</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>Lucky Pickaxe</t>
+          <t>Miner's Lunchbox</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
@@ -3154,24 +2801,24 @@
       </c>
       <c r="N43" s="4" t="inlineStr">
         <is>
-          <t>채굴 시 5% 추가 획득</t>
+          <t>보스 후 HP +5</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>relic_miner_lunchbox</t>
+          <t>relic_leather_handle</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>광산 도시락</t>
+          <t>가죽 손잡이</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>Miner's Lunchbox</t>
+          <t>Leather Handle</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
@@ -3208,24 +2855,24 @@
       </c>
       <c r="N44" s="4" t="inlineStr">
         <is>
-          <t>보스 후 HP +5</t>
+          <t>내구도 소모 -10%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>relic_leather_handle</t>
+          <t>relic_mining_permit</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>가죽 손잡이</t>
+          <t>채굴 허가증</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>Leather Handle</t>
+          <t>Mining Permit</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
@@ -3262,29 +2909,29 @@
       </c>
       <c r="N45" s="4" t="inlineStr">
         <is>
-          <t>내구도 소모 -10%</t>
+          <t>처치 시 20% 철 +1</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>relic_mining_permit</t>
+          <t>relic_auto_repair_kit</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>채굴 허가증</t>
+          <t>자동 수리 키트</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>Mining Permit</t>
+          <t>Auto Repair Kit</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>Tombstone</t>
         </is>
       </c>
       <c r="E46" s="5" t="n">
@@ -3316,24 +2963,24 @@
       </c>
       <c r="N46" s="4" t="inlineStr">
         <is>
-          <t>처치 시 20% 철 +1</t>
+          <t>처치 시 내구도 +1</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>relic_auto_repair_kit</t>
+          <t>relic_vampire_pickaxe</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>자동 수리 키트</t>
+          <t>흡혈 곡괭이</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>Auto Repair Kit</t>
+          <t>Vampire Pickaxe</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
@@ -3370,24 +3017,24 @@
       </c>
       <c r="N47" s="4" t="inlineStr">
         <is>
-          <t>처치 시 내구도 +1</t>
+          <t>채굴 시 10% HP +1</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>relic_vampire_pickaxe</t>
+          <t>relic_ore_sensor</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>흡혈 곡괭이</t>
+          <t>광맥 탐지기</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>Vampire Pickaxe</t>
+          <t>Ore Sensor</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
@@ -3405,7 +3052,7 @@
         <v>0</v>
       </c>
       <c r="H48" s="5" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I48" s="5" t="n">
         <v>0</v>
@@ -3424,24 +3071,24 @@
       </c>
       <c r="N48" s="4" t="inlineStr">
         <is>
-          <t>채굴 시 10% HP +1</t>
+          <t>광물 획득 +30%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>relic_ore_sensor</t>
+          <t>relic_steel_heart</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>광맥 탐지기</t>
+          <t>강철 심장</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>Ore Sensor</t>
+          <t>Steel Heart</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
@@ -3456,10 +3103,10 @@
         <v>0</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H49" s="5" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I49" s="5" t="n">
         <v>0</v>
@@ -3478,24 +3125,24 @@
       </c>
       <c r="N49" s="4" t="inlineStr">
         <is>
-          <t>광물 획득 +30%</t>
+          <t>최대 HP +10</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>relic_steel_heart</t>
+          <t>relic_mine_ring</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>강철 심장</t>
+          <t>광산 반지</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>Steel Heart</t>
+          <t>Mine Ring</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
@@ -3507,10 +3154,10 @@
         <v>0</v>
       </c>
       <c r="F50" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H50" s="5" t="n">
         <v>0</v>
@@ -3532,24 +3179,24 @@
       </c>
       <c r="N50" s="4" t="inlineStr">
         <is>
-          <t>최대 HP +10</t>
+          <t>채굴력 +2</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>relic_mine_ring</t>
+          <t>relic_warrior_necklace</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>광산 반지</t>
+          <t>전사의 목걸이</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>Mine Ring</t>
+          <t>Warrior's Necklace</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
@@ -3558,10 +3205,10 @@
         </is>
       </c>
       <c r="E51" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F51" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G51" s="5" t="n">
         <v>0</v>
@@ -3586,24 +3233,24 @@
       </c>
       <c r="N51" s="4" t="inlineStr">
         <is>
-          <t>채굴력 +2</t>
+          <t>공격력 +2</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>relic_warrior_necklace</t>
+          <t>relic_magma_amulet</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>전사의 목걸이</t>
+          <t>마그마 부적</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>Warrior's Necklace</t>
+          <t>Magma Amulet</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
@@ -3612,7 +3259,7 @@
         </is>
       </c>
       <c r="E52" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F52" s="5" t="n">
         <v>0</v>
@@ -3630,7 +3277,7 @@
         <v>0</v>
       </c>
       <c r="K52" s="5" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L52" s="5" t="n">
         <v>0</v>
@@ -3640,24 +3287,24 @@
       </c>
       <c r="N52" s="4" t="inlineStr">
         <is>
-          <t>공격력 +2</t>
+          <t>화상 면역</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>relic_magma_amulet</t>
+          <t>relic_waterproof_boot</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>마그마 부적</t>
+          <t>방수 장화</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>Magma Amulet</t>
+          <t>Waterproof Boot</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
@@ -3684,7 +3331,7 @@
         <v>0</v>
       </c>
       <c r="K53" s="5" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L53" s="5" t="n">
         <v>0</v>
@@ -3694,24 +3341,24 @@
       </c>
       <c r="N53" s="4" t="inlineStr">
         <is>
-          <t>화상 면역</t>
+          <t>수몰 면역</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>relic_waterproof_boot</t>
+          <t>relic_poison_antidote</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>방수 장화</t>
+          <t>독 해독제</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>Waterproof Boot</t>
+          <t>Poison Antidote</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
@@ -3748,24 +3395,24 @@
       </c>
       <c r="N54" s="4" t="inlineStr">
         <is>
-          <t>수몰 면역</t>
+          <t>중독 면역</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>relic_poison_antidote</t>
+          <t>relic_greedy_coin</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>독 해독제</t>
+          <t>탐욕의 동전</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>Poison Antidote</t>
+          <t>Greedy Coin</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
@@ -3783,7 +3430,7 @@
         <v>0</v>
       </c>
       <c r="H55" s="5" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I55" s="5" t="n">
         <v>0</v>
@@ -3802,24 +3449,24 @@
       </c>
       <c r="N55" s="4" t="inlineStr">
         <is>
-          <t>중독 면역</t>
+          <t>광물 획득 +50%  모든 회복량 -50%</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>relic_greedy_coin</t>
+          <t>relic_cursed_digger</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>탐욕의 동전</t>
+          <t>저주받은 곡괭이</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>Greedy Coin</t>
+          <t>Cursed Digger</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
@@ -3831,13 +3478,13 @@
         <v>0</v>
       </c>
       <c r="F56" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="H56" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I56" s="5" t="n">
         <v>0</v>
@@ -3856,24 +3503,24 @@
       </c>
       <c r="N56" s="4" t="inlineStr">
         <is>
-          <t>광물 획득 +50%  모든 회복량 -50%</t>
+          <t>채굴력 +3  최대 HP -10</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>relic_cursed_digger</t>
+          <t>relic_elite_hunter_medal</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>저주받은 곡괭이</t>
+          <t>엘리트 헌터 훈장</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>Cursed Digger</t>
+          <t>Elite Hunter Medal</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
@@ -3885,10 +3532,10 @@
         <v>0</v>
       </c>
       <c r="F57" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="H57" s="5" t="n">
         <v>0</v>
@@ -3910,24 +3557,24 @@
       </c>
       <c r="N57" s="4" t="inlineStr">
         <is>
-          <t>채굴력 +3  최대 HP -10</t>
+          <t>엘리트 처치 시 유물 추가</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>relic_elite_hunter_medal</t>
+          <t>relic_god_pickaxe</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>엘리트 헌터 훈장</t>
+          <t>신의 곡괭이</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>Elite Hunter Medal</t>
+          <t>God's Pickaxe</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
@@ -3939,7 +3586,7 @@
         <v>0</v>
       </c>
       <c r="F58" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G58" s="5" t="n">
         <v>0</v>
@@ -3964,24 +3611,24 @@
       </c>
       <c r="N58" s="4" t="inlineStr">
         <is>
-          <t>엘리트 처치 시 유물 추가</t>
+          <t>채굴력 +5  내구도 감소 없음</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>relic_god_pickaxe</t>
+          <t>relic_mine_crown</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>신의 곡괭이</t>
+          <t>광산 왕관</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>God's Pickaxe</t>
+          <t>Mine Crown</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
@@ -3993,13 +3640,13 @@
         <v>0</v>
       </c>
       <c r="F59" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G59" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H59" s="5" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I59" s="5" t="n">
         <v>0</v>
@@ -4018,24 +3665,24 @@
       </c>
       <c r="N59" s="4" t="inlineStr">
         <is>
-          <t>채굴력 +5  내구도 감소 없음</t>
+          <t>모든 광물 획득량 2배</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>relic_mine_crown</t>
+          <t>relic_immortal_heart</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>광산 왕관</t>
+          <t>불사의 심장</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>Mine Crown</t>
+          <t>Immortal Heart</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
@@ -4053,7 +3700,7 @@
         <v>0</v>
       </c>
       <c r="H60" s="5" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I60" s="5" t="n">
         <v>0</v>
@@ -4072,24 +3719,24 @@
       </c>
       <c r="N60" s="4" t="inlineStr">
         <is>
-          <t>모든 광물 획득량 2배</t>
+          <t>1회 부활 (HP 30%)</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>relic_immortal_heart</t>
+          <t>relic_soul_contract</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>불사의 심장</t>
+          <t>영혼 계약서</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>Immortal Heart</t>
+          <t>Soul Contract</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
@@ -4098,13 +3745,13 @@
         </is>
       </c>
       <c r="E61" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F61" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="H61" s="5" t="n">
         <v>0</v>
@@ -4126,24 +3773,24 @@
       </c>
       <c r="N61" s="4" t="inlineStr">
         <is>
-          <t>1회 부활 (HP 30%)</t>
+          <t>공격력 +5  최대 HP -20</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>relic_soul_contract</t>
+          <t>relic_dragon_fang</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>영혼 계약서</t>
+          <t>드래곤 송곳니</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>Soul Contract</t>
+          <t>Dragon Fang</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
@@ -4152,13 +3799,13 @@
         </is>
       </c>
       <c r="E62" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F62" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="H62" s="5" t="n">
         <v>0</v>
@@ -4180,24 +3827,24 @@
       </c>
       <c r="N62" s="4" t="inlineStr">
         <is>
-          <t>공격력 +5  최대 HP -20</t>
+          <t>몬스터 피해 +50%</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>relic_dragon_fang</t>
+          <t>relic_infinite_whetstone</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>드래곤 송곳니</t>
+          <t>무한 숫돌</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>Dragon Fang</t>
+          <t>Infinite Whetstone</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
@@ -4234,24 +3881,24 @@
       </c>
       <c r="N63" s="4" t="inlineStr">
         <is>
-          <t>몬스터 피해 +50%</t>
+          <t>내구도 감소 없음</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>relic_infinite_whetstone</t>
+          <t>relic_mine_blessing</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>무한 숫돌</t>
+          <t>광산 신의 축복</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>Infinite Whetstone</t>
+          <t>Mine God's Blessing</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
@@ -4260,13 +3907,13 @@
         </is>
       </c>
       <c r="E64" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F64" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H64" s="5" t="n">
         <v>0</v>
@@ -4288,24 +3935,24 @@
       </c>
       <c r="N64" s="4" t="inlineStr">
         <is>
-          <t>내구도 감소 없음</t>
+          <t>공격력 +3  채굴력 +3  최대 HP +3</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>relic_mine_blessing</t>
+          <t>relic_golden_bag</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>광산 신의 축복</t>
+          <t>황금 주머니</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>Mine God's Blessing</t>
+          <t>Golden Bag</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
@@ -4314,16 +3961,16 @@
         </is>
       </c>
       <c r="E65" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F65" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H65" s="5" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I65" s="5" t="n">
         <v>0</v>
@@ -4342,24 +3989,24 @@
       </c>
       <c r="N65" s="4" t="inlineStr">
         <is>
-          <t>공격력 +3  채굴력 +3  최대 HP +3</t>
+          <t>광물 획득 +50%</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>relic_golden_bag</t>
+          <t>relic_hourglass</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>황금 주머니</t>
+          <t>시간의 모래시계</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>Golden Bag</t>
+          <t>Hourglass of Time</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
@@ -4377,7 +4024,7 @@
         <v>0</v>
       </c>
       <c r="H66" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I66" s="5" t="n">
         <v>0</v>
@@ -4396,24 +4043,24 @@
       </c>
       <c r="N66" s="4" t="inlineStr">
         <is>
-          <t>광물 획득 +50%</t>
+          <t>보스 처치 시 HP 전부 회복</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>relic_hourglass</t>
+          <t>relic_abyssal_core</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>시간의 모래시계</t>
+          <t>심연의 핵</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>Hourglass of Time</t>
+          <t>Abyssal Core</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
@@ -4450,29 +4097,29 @@
       </c>
       <c r="N67" s="4" t="inlineStr">
         <is>
-          <t>보스 처치 시 HP 전부 회복</t>
+          <t>엘리트 보상 2배  유물 추가</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>relic_abyssal_core</t>
+          <t>relic_stone_blessing</t>
         </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>심연의 핵</t>
+          <t>바위의 축복</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>Abyssal Core</t>
+          <t>Stone's Blessing</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>Tombstone</t>
+          <t>Common</t>
         </is>
       </c>
       <c r="E68" s="5" t="n">
@@ -4504,24 +4151,24 @@
       </c>
       <c r="N68" s="4" t="inlineStr">
         <is>
-          <t>엘리트 보상 2배  유물 추가</t>
+          <t>채굴 완료 시 10% 확률로 같은 광물 +1개 획득</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>relic_stone_blessing</t>
+          <t>relic_miner_backpack</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>바위의 축복</t>
+          <t>광부의 배낭</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>Stone's Blessing</t>
+          <t>Miner's Backpack</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
@@ -4558,24 +4205,24 @@
       </c>
       <c r="N69" s="4" t="inlineStr">
         <is>
-          <t>채굴 완료 시 10% 확률로 같은 광물 +1개 획득</t>
+          <t>인벤토리 사이즈 +10</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>relic_miner_backpack</t>
+          <t>relic_mining_gloves</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>광부의 배낭</t>
+          <t>채굴 장갑</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>Miner's Backpack</t>
+          <t>Mining Gloves</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
@@ -4593,7 +4240,7 @@
         <v>0</v>
       </c>
       <c r="H70" s="5" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I70" s="5" t="n">
         <v>0</v>
@@ -4612,24 +4259,24 @@
       </c>
       <c r="N70" s="4" t="inlineStr">
         <is>
-          <t>인벤토리 사이즈 +10</t>
+          <t>광물 획득량 +10%</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>relic_mining_gloves</t>
+          <t>relic_war_medal</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>채굴 장갑</t>
+          <t>전쟁의 메달</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>Mining Gloves</t>
+          <t>War Medal</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
@@ -4638,7 +4285,7 @@
         </is>
       </c>
       <c r="E71" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F71" s="5" t="n">
         <v>0</v>
@@ -4647,7 +4294,7 @@
         <v>0</v>
       </c>
       <c r="H71" s="5" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I71" s="5" t="n">
         <v>0</v>
@@ -4666,24 +4313,24 @@
       </c>
       <c r="N71" s="4" t="inlineStr">
         <is>
-          <t>광물 획득량 +10%</t>
+          <t>공격력 +2</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>relic_war_medal</t>
+          <t>relic_reinforced_whetstone</t>
         </is>
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>전쟁의 메달</t>
+          <t>강화 숫돌</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>War Medal</t>
+          <t>Reinforced Whetstone</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
@@ -4692,7 +4339,7 @@
         </is>
       </c>
       <c r="E72" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F72" s="5" t="n">
         <v>0</v>
@@ -4720,24 +4367,24 @@
       </c>
       <c r="N72" s="4" t="inlineStr">
         <is>
-          <t>공격력 +2</t>
+          <t>곡괭이 내구도 최대치 +20</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
-          <t>relic_reinforced_whetstone</t>
+          <t>relic_nail_pouch</t>
         </is>
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>강화 숫돌</t>
+          <t>철못 주머니</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>Reinforced Whetstone</t>
+          <t>Nail Pouch</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
@@ -4774,24 +4421,24 @@
       </c>
       <c r="N73" s="4" t="inlineStr">
         <is>
-          <t>곡괭이 내구도 최대치 +20</t>
+          <t>곡괭이 내구도 감소량 10% 감소</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>relic_nail_pouch</t>
+          <t>relic_alchemy_notebook</t>
         </is>
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>철못 주머니</t>
+          <t>연금술 노트</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>Nail Pouch</t>
+          <t>Alchemy Notebook</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
@@ -4828,24 +4475,24 @@
       </c>
       <c r="N74" s="4" t="inlineStr">
         <is>
-          <t>곡괭이 내구도 감소량 10% 감소</t>
+          <t>포션 효과 +20%</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>relic_alchemy_notebook</t>
+          <t>relic_healing_herb</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>연금술 노트</t>
+          <t>회복 허브</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>Alchemy Notebook</t>
+          <t>Healing Herb</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
@@ -4882,24 +4529,24 @@
       </c>
       <c r="N75" s="4" t="inlineStr">
         <is>
-          <t>포션 효과 +20%</t>
+          <t>전투 종료 시 체력회복 +2</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>relic_healing_herb</t>
+          <t>relic_holy_symbol</t>
         </is>
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>회복 허브</t>
+          <t>신성한 상징</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>Healing Herb</t>
+          <t>Holy Symbol</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
@@ -4926,7 +4573,7 @@
         <v>0</v>
       </c>
       <c r="K76" s="5" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L76" s="5" t="n">
         <v>0</v>
@@ -4936,24 +4583,24 @@
       </c>
       <c r="N76" s="4" t="inlineStr">
         <is>
-          <t>전투 종료 시 체력회복 +2</t>
+          <t>화상, 독 데미지 무효</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>relic_holy_symbol</t>
+          <t>relic_old_map</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>신성한 상징</t>
+          <t>오래된 지도</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>Holy Symbol</t>
+          <t>Old Map</t>
         </is>
       </c>
       <c r="D77" s="5" t="inlineStr">
@@ -4968,7 +4615,7 @@
         <v>0</v>
       </c>
       <c r="G77" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H77" s="5" t="n">
         <v>0</v>
@@ -4980,7 +4627,7 @@
         <v>0</v>
       </c>
       <c r="K77" s="5" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L77" s="5" t="n">
         <v>0</v>
@@ -4990,24 +4637,24 @@
       </c>
       <c r="N77" s="4" t="inlineStr">
         <is>
-          <t>화상, 독 데미지 무효</t>
+          <t>이벤트 노드 도착 시 최대 체력 +1, 체력 3 회복</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>relic_old_map</t>
+          <t>relic_explorers_journal</t>
         </is>
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>오래된 지도</t>
+          <t>탐험가의 일지</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>Old Map</t>
+          <t>Explorer's Journal</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
@@ -5016,13 +4663,13 @@
         </is>
       </c>
       <c r="E78" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F78" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G78" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H78" s="5" t="n">
         <v>0</v>
@@ -5044,24 +4691,24 @@
       </c>
       <c r="N78" s="4" t="inlineStr">
         <is>
-          <t>이벤트 노드 도착 시 최대 체력 +1, 체력 3 회복</t>
+          <t>이벤트 노드 도착 시 공격력 +2</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
         <is>
-          <t>relic_explorers_journal</t>
+          <t>relic_constellation_compass</t>
         </is>
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>탐험가의 일지</t>
+          <t>별자리 나침반</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>Explorer's Journal</t>
+          <t>Constellation Compass</t>
         </is>
       </c>
       <c r="D79" s="5" t="inlineStr">
@@ -5070,11 +4717,11 @@
         </is>
       </c>
       <c r="E79" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F79" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="F79" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="G79" s="5" t="n">
         <v>0</v>
       </c>
@@ -5098,24 +4745,24 @@
       </c>
       <c r="N79" s="4" t="inlineStr">
         <is>
-          <t>이벤트 노드 도착 시 공격력 +2</t>
+          <t>이벤트 노드 완료 시 채굴력 +2</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
         <is>
-          <t>relic_constellation_compass</t>
+          <t>relic_treasure_detector</t>
         </is>
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>별자리 나침반</t>
+          <t>보물 감지기</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>Constellation Compass</t>
+          <t>Treasure Detector</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
@@ -5124,13 +4771,13 @@
         </is>
       </c>
       <c r="E80" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F80" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G80" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H80" s="5" t="n">
         <v>0</v>
@@ -5152,24 +4799,24 @@
       </c>
       <c r="N80" s="4" t="inlineStr">
         <is>
-          <t>이벤트 노드 완료 시 채굴력 +2</t>
+          <t>보물상자 노드 도착 시 최대 체력 +1, 공격력 +1</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>relic_treasure_detector</t>
+          <t>relic_ancient_key</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>보물 감지기</t>
+          <t>고대 열쇠</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>Treasure Detector</t>
+          <t>Ancient Key</t>
         </is>
       </c>
       <c r="D81" s="5" t="inlineStr">
@@ -5178,13 +4825,13 @@
         </is>
       </c>
       <c r="E81" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F81" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G81" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H81" s="5" t="n">
         <v>0</v>
@@ -5206,24 +4853,24 @@
       </c>
       <c r="N81" s="4" t="inlineStr">
         <is>
-          <t>보물상자 노드 도착 시 최대 체력 +1, 공격력 +1</t>
+          <t>보물상자 노드 완료 시 무작위 포션 1개 획득</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
         <is>
-          <t>relic_ancient_key</t>
+          <t>relic_lucky_compass</t>
         </is>
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>고대 열쇠</t>
+          <t>행운의 나침반</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>Ancient Key</t>
+          <t>Lucky Compass</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
@@ -5260,24 +4907,24 @@
       </c>
       <c r="N82" s="4" t="inlineStr">
         <is>
-          <t>보물상자 노드 완료 시 무작위 포션 1개 획득</t>
+          <t>맵에서 이벤트 노드 등장 확률 증가</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>relic_lucky_compass</t>
+          <t>relic_golden_compass</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>행운의 나침반</t>
+          <t>황금 나침반</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>Lucky Compass</t>
+          <t>Golden Compass</t>
         </is>
       </c>
       <c r="D83" s="5" t="inlineStr">
@@ -5314,24 +4961,24 @@
       </c>
       <c r="N83" s="4" t="inlineStr">
         <is>
-          <t>맵에서 이벤트 노드 등장 확률 증가</t>
+          <t>맵에서 보물상자 노드 등장 확률 증가</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>relic_golden_compass</t>
+          <t>relic_travelers_backpack</t>
         </is>
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>황금 나침반</t>
+          <t>여행자의 배낭</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>Golden Compass</t>
+          <t>Traveler's Backpack</t>
         </is>
       </c>
       <c r="D84" s="5" t="inlineStr">
@@ -5368,24 +5015,24 @@
       </c>
       <c r="N84" s="4" t="inlineStr">
         <is>
-          <t>맵에서 보물상자 노드 등장 확률 증가</t>
+          <t>소비 아이템 사용 시 1턴간 공격력 +2 (최대 2중첩)</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>relic_travelers_backpack</t>
+          <t>relic_golden_flask</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>여행자의 배낭</t>
+          <t>황금 플라스크</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>Traveler's Backpack</t>
+          <t>Golden Flask</t>
         </is>
       </c>
       <c r="D85" s="5" t="inlineStr">
@@ -5422,24 +5069,24 @@
       </c>
       <c r="N85" s="4" t="inlineStr">
         <is>
-          <t>소비 아이템 사용 시 1턴간 공격력 +2 (최대 2중첩)</t>
+          <t>포션 사용 시 1턴간 공격력 +3 (최대 3중첩)</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>relic_golden_flask</t>
+          <t>relic_mysterious_serum</t>
         </is>
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>황금 플라스크</t>
+          <t>신비한 시약</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>Golden Flask</t>
+          <t>Mysterious Serum</t>
         </is>
       </c>
       <c r="D86" s="5" t="inlineStr">
@@ -5476,24 +5123,24 @@
       </c>
       <c r="N86" s="4" t="inlineStr">
         <is>
-          <t>포션 사용 시 1턴간 공격력 +3 (최대 3중첩)</t>
+          <t>소비 아이템 사용 시 체력 1 회복</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
-          <t>relic_mysterious_serum</t>
+          <t>relic_ring_of_blessing</t>
         </is>
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>신비한 시약</t>
+          <t>축복의 반지</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>Mysterious Serum</t>
+          <t>Ring of Blessing</t>
         </is>
       </c>
       <c r="D87" s="5" t="inlineStr">
@@ -5530,24 +5177,24 @@
       </c>
       <c r="N87" s="4" t="inlineStr">
         <is>
-          <t>소비 아이템 사용 시 체력 1 회복</t>
+          <t>포션 사용 시 화상과 중독 제거</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
         <is>
-          <t>relic_ring_of_blessing</t>
+          <t>relic_emergency_kit</t>
         </is>
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>축복의 반지</t>
+          <t>응급 키트</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>Ring of Blessing</t>
+          <t>Emergency Kit</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr">
@@ -5584,24 +5231,24 @@
       </c>
       <c r="N88" s="4" t="inlineStr">
         <is>
-          <t>포션 사용 시 화상과 중독 제거</t>
+          <t>체력이 30% 이하일 때 포션 회복량 2배</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
         <is>
-          <t>relic_emergency_kit</t>
+          <t>relic_battle_axe</t>
         </is>
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>응급 키트</t>
+          <t>전투 도끼</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>Emergency Kit</t>
+          <t>Battle Axe</t>
         </is>
       </c>
       <c r="D89" s="5" t="inlineStr">
@@ -5638,24 +5285,24 @@
       </c>
       <c r="N89" s="4" t="inlineStr">
         <is>
-          <t>체력이 30% 이하일 때 포션 회복량 2배</t>
+          <t>전투 중 첫 공격 피해 +30% (전투당 1회)</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>relic_battle_axe</t>
+          <t>relic_battle_gauntlet</t>
         </is>
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>전투 도끼</t>
+          <t>전투 장갑</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>Battle Axe</t>
+          <t>Battle Gauntlet</t>
         </is>
       </c>
       <c r="D90" s="5" t="inlineStr">
@@ -5692,24 +5339,24 @@
       </c>
       <c r="N90" s="4" t="inlineStr">
         <is>
-          <t>전투 중 첫 공격 피해 +30% (전투당 1회)</t>
+          <t>전투 중 경과한 턴마다 공격력 +1 누적</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>relic_battle_gauntlet</t>
+          <t>relic_steel_armor</t>
         </is>
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>전투 장갑</t>
+          <t>강철 갑옷</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>Battle Gauntlet</t>
+          <t>Steel Armor</t>
         </is>
       </c>
       <c r="D91" s="5" t="inlineStr">
@@ -5746,24 +5393,24 @@
       </c>
       <c r="N91" s="4" t="inlineStr">
         <is>
-          <t>전투 중 경과한 턴마다 공격력 +1 누적</t>
+          <t>전투 첫 턴에 방어도 +3</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>relic_steel_armor</t>
+          <t>relic_battle_flag</t>
         </is>
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>강철 갑옷</t>
+          <t>전장의 깃발</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>Steel Armor</t>
+          <t>Battle Flag</t>
         </is>
       </c>
       <c r="D92" s="5" t="inlineStr">
@@ -5800,24 +5447,24 @@
       </c>
       <c r="N92" s="4" t="inlineStr">
         <is>
-          <t>전투 첫 턴에 방어도 +3</t>
+          <t>조우 중인 몬스터 1마리당 공격력 +2</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
-          <t>relic_battle_flag</t>
+          <t>relic_bracelet_of_rage</t>
         </is>
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>전장의 깃발</t>
+          <t>분노의 팔찌</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>Battle Flag</t>
+          <t>Bracelet of Rage</t>
         </is>
       </c>
       <c r="D93" s="5" t="inlineStr">
@@ -5854,24 +5501,24 @@
       </c>
       <c r="N93" s="4" t="inlineStr">
         <is>
-          <t>조우 중인 몬스터 1마리당 공격력 +2</t>
+          <t>전투 중 실제 체력 피해를 입을 때마다 공격력 +2 누적</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t>relic_bracelet_of_rage</t>
+          <t>relic_paladins_cloak</t>
         </is>
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>분노의 팔찌</t>
+          <t>성기사의 망토</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>Bracelet of Rage</t>
+          <t>Paladin's Cloak</t>
         </is>
       </c>
       <c r="D94" s="5" t="inlineStr">
@@ -5908,24 +5555,24 @@
       </c>
       <c r="N94" s="4" t="inlineStr">
         <is>
-          <t>전투 중 실제 체력 피해를 입을 때마다 공격력 +2 누적</t>
+          <t>전투 중 매 턴 시작 시 방어도 +5</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
         <is>
-          <t>relic_paladins_cloak</t>
+          <t>relic_blood_necklace</t>
         </is>
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>성기사의 망토</t>
+          <t>피의 목걸이</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>Paladin's Cloak</t>
+          <t>Blood Necklace</t>
         </is>
       </c>
       <c r="D95" s="5" t="inlineStr">
@@ -5962,24 +5609,24 @@
       </c>
       <c r="N95" s="4" t="inlineStr">
         <is>
-          <t>전투 중 매 턴 시작 시 방어도 +5</t>
+          <t>몬스터 처치 시 체력 1 회복</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="4" t="inlineStr">
         <is>
-          <t>relic_blood_necklace</t>
+          <t>relic_blood_ring</t>
         </is>
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>피의 목걸이</t>
+          <t>핏빛 반지</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>Blood Necklace</t>
+          <t>Blood Ring</t>
         </is>
       </c>
       <c r="D96" s="5" t="inlineStr">
@@ -6016,24 +5663,24 @@
       </c>
       <c r="N96" s="4" t="inlineStr">
         <is>
-          <t>몬스터 처치 시 체력 1 회복</t>
+          <t>몬스터에게 피해를 입힐 때마다 체력 1 회복</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
         <is>
-          <t>relic_blood_ring</t>
+          <t>relic_hunters_medal</t>
         </is>
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>핏빛 반지</t>
+          <t>사냥꾼의 훈장</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>Blood Ring</t>
+          <t>Hunter's Medal</t>
         </is>
       </c>
       <c r="D97" s="5" t="inlineStr">
@@ -6070,24 +5717,24 @@
       </c>
       <c r="N97" s="4" t="inlineStr">
         <is>
-          <t>몬스터에게 피해를 입힐 때마다 체력 1 회복</t>
+          <t>엘리트 몬스터 처치 시 포션 추가 드롭</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="4" t="inlineStr">
         <is>
-          <t>relic_hunters_medal</t>
+          <t>relic_maintenance_kit</t>
         </is>
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>사냥꾼의 훈장</t>
+          <t>정비 키트</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>Hunter's Medal</t>
+          <t>Maintenance Kit</t>
         </is>
       </c>
       <c r="D98" s="5" t="inlineStr">
@@ -6124,24 +5771,24 @@
       </c>
       <c r="N98" s="4" t="inlineStr">
         <is>
-          <t>엘리트 몬스터 처치 시 포션 추가 드롭</t>
+          <t>엘리트 또는 보스 처치 시 곡괭이 내구도 완전 회복</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="4" t="inlineStr">
         <is>
-          <t>relic_maintenance_kit</t>
+          <t>relic_alloy_handle</t>
         </is>
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>정비 키트</t>
+          <t>합금 손잡이</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>Maintenance Kit</t>
+          <t>Alloy Handle</t>
         </is>
       </c>
       <c r="D99" s="5" t="inlineStr">
@@ -6178,24 +5825,24 @@
       </c>
       <c r="N99" s="4" t="inlineStr">
         <is>
-          <t>엘리트 또는 보스 처치 시 곡괭이 내구도 완전 회복</t>
+          <t>곡괭이 수리 시 체력 2 회복</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="4" t="inlineStr">
         <is>
-          <t>relic_alloy_handle</t>
+          <t>relic_furnace_core</t>
         </is>
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>합금 손잡이</t>
+          <t>용광로 코어</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>Alloy Handle</t>
+          <t>Furnace Core</t>
         </is>
       </c>
       <c r="D100" s="5" t="inlineStr">
@@ -6232,24 +5879,24 @@
       </c>
       <c r="N100" s="4" t="inlineStr">
         <is>
-          <t>곡괭이 수리 시 체력 2 회복</t>
+          <t>곡괭이 수리 시 10% 확률로 최대 내구도 영구 +1</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
         <is>
-          <t>relic_furnace_core</t>
+          <t>relic_steel_hammer</t>
         </is>
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>용광로 코어</t>
+          <t>강철 망치</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>Furnace Core</t>
+          <t>Steel Hammer</t>
         </is>
       </c>
       <c r="D101" s="5" t="inlineStr">
@@ -6286,24 +5933,24 @@
       </c>
       <c r="N101" s="4" t="inlineStr">
         <is>
-          <t>곡괭이 수리 시 10% 확률로 최대 내구도 영구 +1</t>
+          <t>곡괭이 수리 효율 +50%</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="4" t="inlineStr">
         <is>
-          <t>relic_steel_hammer</t>
+          <t>relic_reinforced_pickaxe_handle</t>
         </is>
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>강철 망치</t>
+          <t>강화 곡괭이 손잡이</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>Steel Hammer</t>
+          <t>Reinforced Pickaxe Handle</t>
         </is>
       </c>
       <c r="D102" s="5" t="inlineStr">
@@ -6340,24 +5987,24 @@
       </c>
       <c r="N102" s="4" t="inlineStr">
         <is>
-          <t>곡괭이 수리 효율 +50%</t>
+          <t>보유 광물 9개당 채굴력 +1</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="4" t="inlineStr">
         <is>
-          <t>relic_reinforced_pickaxe_handle</t>
+          <t>relic_pickaxe_sword</t>
         </is>
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>강화 곡괭이 손잡이</t>
+          <t>곡괭이 검</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>Reinforced Pickaxe Handle</t>
+          <t>Pickaxe Sword</t>
         </is>
       </c>
       <c r="D103" s="5" t="inlineStr">
@@ -6394,24 +6041,24 @@
       </c>
       <c r="N103" s="4" t="inlineStr">
         <is>
-          <t>보유 광물 9개당 채굴력 +1</t>
+          <t>채굴력 3당 공격력 +1</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="4" t="inlineStr">
         <is>
-          <t>relic_pickaxe_sword</t>
+          <t>relic_deep_breath</t>
         </is>
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>곡괭이 검</t>
+          <t>깊은 숨결</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>Pickaxe Sword</t>
+          <t>Deep Breath</t>
         </is>
       </c>
       <c r="D104" s="5" t="inlineStr">
@@ -6448,24 +6095,24 @@
       </c>
       <c r="N104" s="4" t="inlineStr">
         <is>
-          <t>채굴력 3당 공격력 +1</t>
+          <t>깊이 50m당 채굴력 +2</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="4" t="inlineStr">
         <is>
-          <t>relic_deep_breath</t>
+          <t>relic_whetstone_blade</t>
         </is>
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>깊은 숨결</t>
+          <t>숫돌 칼날</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>Deep Breath</t>
+          <t>Whetstone Blade</t>
         </is>
       </c>
       <c r="D105" s="5" t="inlineStr">
@@ -6502,24 +6149,24 @@
       </c>
       <c r="N105" s="4" t="inlineStr">
         <is>
-          <t>깊이 50m당 채굴력 +2</t>
+          <t>곡괭이 내구도에 비례해 공격력 증가</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="4" t="inlineStr">
         <is>
-          <t>relic_whetstone_blade</t>
+          <t>relic_berserkers_axe</t>
         </is>
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>숫돌 칼날</t>
+          <t>광전사의 도끼</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr">
         <is>
-          <t>Whetstone Blade</t>
+          <t>Berserker's Axe</t>
         </is>
       </c>
       <c r="D106" s="5" t="inlineStr">
@@ -6556,24 +6203,24 @@
       </c>
       <c r="N106" s="4" t="inlineStr">
         <is>
-          <t>곡괭이 내구도에 비례해 공격력 증가</t>
+          <t>잃은 체력 10%당 공격력 +1</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="4" t="inlineStr">
         <is>
-          <t>relic_berserkers_axe</t>
+          <t>relic_blood_pact</t>
         </is>
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>광전사의 도끼</t>
+          <t>피의 계약</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>Berserker's Axe</t>
+          <t>Blood Pact</t>
         </is>
       </c>
       <c r="D107" s="5" t="inlineStr">
@@ -6610,24 +6257,24 @@
       </c>
       <c r="N107" s="4" t="inlineStr">
         <is>
-          <t>잃은 체력 10%당 공격력 +1</t>
+          <t>체력 50% 이하일 때 피해 +10%</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="4" t="inlineStr">
         <is>
-          <t>relic_blood_pact</t>
+          <t>relic_red_heart</t>
         </is>
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>피의 계약</t>
+          <t>붉은 심장</t>
         </is>
       </c>
       <c r="C108" s="4" t="inlineStr">
         <is>
-          <t>Blood Pact</t>
+          <t>Red Heart</t>
         </is>
       </c>
       <c r="D108" s="5" t="inlineStr">
@@ -6664,24 +6311,24 @@
       </c>
       <c r="N108" s="4" t="inlineStr">
         <is>
-          <t>체력 50% 이하일 때 피해 +10%</t>
+          <t>체력 30% 이하일 때 피해 +20%</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="4" t="inlineStr">
         <is>
-          <t>relic_red_heart</t>
+          <t>relic_distillation_device</t>
         </is>
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>붉은 심장</t>
+          <t>증류 장치</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>Red Heart</t>
+          <t>Distillation Device</t>
         </is>
       </c>
       <c r="D109" s="5" t="inlineStr">
@@ -6718,24 +6365,24 @@
       </c>
       <c r="N109" s="4" t="inlineStr">
         <is>
-          <t>체력 30% 이하일 때 피해 +20%</t>
+          <t>상점의 포션 가격이 뿌리 2개만큼 저렴해짐</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="4" t="inlineStr">
         <is>
-          <t>relic_distillation_device</t>
+          <t>relic_golden_ticket</t>
         </is>
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>증류 장치</t>
+          <t>황금 티켓</t>
         </is>
       </c>
       <c r="C110" s="4" t="inlineStr">
         <is>
-          <t>Distillation Device</t>
+          <t>Golden Ticket</t>
         </is>
       </c>
       <c r="D110" s="5" t="inlineStr">
@@ -6772,24 +6419,24 @@
       </c>
       <c r="N110" s="4" t="inlineStr">
         <is>
-          <t>상점의 포션 가격이 뿌리 2개만큼 저렴해짐</t>
+          <t>상점의 모든 가격 -15%</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="4" t="inlineStr">
         <is>
-          <t>relic_golden_ticket</t>
+          <t>relic_holy_water_bottle</t>
         </is>
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>황금 티켓</t>
+          <t>성수병</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>Golden Ticket</t>
+          <t>Holy Water Bottle</t>
         </is>
       </c>
       <c r="D111" s="5" t="inlineStr">
@@ -6810,7 +6457,7 @@
         <v>0</v>
       </c>
       <c r="I111" s="5" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="J111" s="5" t="n">
         <v>0</v>
@@ -6826,24 +6473,24 @@
       </c>
       <c r="N111" s="4" t="inlineStr">
         <is>
-          <t>상점의 모든 가격 -15%</t>
+          <t>화상, 중독 지속시간 -1턴</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="4" t="inlineStr">
         <is>
-          <t>relic_holy_water_bottle</t>
+          <t>relic_blessed_shield</t>
         </is>
       </c>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t>성수병</t>
+          <t>축복의 방패</t>
         </is>
       </c>
       <c r="C112" s="4" t="inlineStr">
         <is>
-          <t>Holy Water Bottle</t>
+          <t>Blessed Shield</t>
         </is>
       </c>
       <c r="D112" s="5" t="inlineStr">
@@ -6864,7 +6511,7 @@
         <v>0</v>
       </c>
       <c r="I112" s="5" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="J112" s="5" t="n">
         <v>0</v>
@@ -6880,24 +6527,24 @@
       </c>
       <c r="N112" s="4" t="inlineStr">
         <is>
-          <t>화상, 중독 지속시간 -1턴</t>
+          <t>상태이상으로 받는 피해 -10%</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="4" t="inlineStr">
         <is>
-          <t>relic_blessed_shield</t>
+          <t>relic_chalice_of_purification</t>
         </is>
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>축복의 방패</t>
+          <t>정화의 성배</t>
         </is>
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>Blessed Shield</t>
+          <t>Chalice of Purification</t>
         </is>
       </c>
       <c r="D113" s="5" t="inlineStr">
@@ -6934,24 +6581,24 @@
       </c>
       <c r="N113" s="4" t="inlineStr">
         <is>
-          <t>상태이상으로 받는 피해 -10%</t>
+          <t>전투 종료 시 모든 디버프 제거</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="4" t="inlineStr">
         <is>
-          <t>relic_chalice_of_purification</t>
+          <t>relic_ring_of_luck</t>
         </is>
       </c>
       <c r="B114" s="4" t="inlineStr">
         <is>
-          <t>정화의 성배</t>
+          <t>행운의 반지</t>
         </is>
       </c>
       <c r="C114" s="4" t="inlineStr">
         <is>
-          <t>Chalice of Purification</t>
+          <t>Ring of Luck</t>
         </is>
       </c>
       <c r="D114" s="5" t="inlineStr">
@@ -6988,24 +6635,24 @@
       </c>
       <c r="N114" s="4" t="inlineStr">
         <is>
-          <t>전투 종료 시 모든 디버프 제거</t>
+          <t>Rare 이상 유물 등장 확률 +10%</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="4" t="inlineStr">
         <is>
-          <t>relic_ring_of_luck</t>
+          <t>relic_mysterious_key</t>
         </is>
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>행운의 반지</t>
+          <t>신비한 열쇠</t>
         </is>
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>Ring of Luck</t>
+          <t>Mysterious Key</t>
         </is>
       </c>
       <c r="D115" s="5" t="inlineStr">
@@ -7042,24 +6689,24 @@
       </c>
       <c r="N115" s="4" t="inlineStr">
         <is>
-          <t>Rare 이상 유물 등장 확률 +10%</t>
+          <t>보물상자에서 Rare 유물이 나올 가중치 증가</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="4" t="inlineStr">
         <is>
-          <t>relic_mysterious_key</t>
+          <t>relic_golden_prayer_book</t>
         </is>
       </c>
       <c r="B116" s="4" t="inlineStr">
         <is>
-          <t>신비한 열쇠</t>
+          <t>황금의 기도서</t>
         </is>
       </c>
       <c r="C116" s="4" t="inlineStr">
         <is>
-          <t>Mysterious Key</t>
+          <t>Golden Prayer Book</t>
         </is>
       </c>
       <c r="D116" s="5" t="inlineStr">
@@ -7096,24 +6743,24 @@
       </c>
       <c r="N116" s="4" t="inlineStr">
         <is>
-          <t>보물상자에서 Rare 유물이 나올 가중치 증가</t>
+          <t>이번 전투에서 상태이상으로 입은 피해량만큼 공격력 증가</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="4" t="inlineStr">
         <is>
-          <t>relic_golden_prayer_book</t>
+          <t>relic_collectors_bag</t>
         </is>
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>황금의 기도서</t>
+          <t>수집가의 가방</t>
         </is>
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>Golden Prayer Book</t>
+          <t>Collector's Bag</t>
         </is>
       </c>
       <c r="D117" s="5" t="inlineStr">
@@ -7150,24 +6797,24 @@
       </c>
       <c r="N117" s="4" t="inlineStr">
         <is>
-          <t>이번 전투에서 상태이상으로 입은 피해량만큼 공격력 증가</t>
+          <t>획득 즉시 보유 중인 다른 유물 1개의 효과를 복사한다</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="4" t="inlineStr">
         <is>
-          <t>relic_collectors_bag</t>
+          <t>relic_grave_robbers_gloves</t>
         </is>
       </c>
       <c r="B118" s="4" t="inlineStr">
         <is>
-          <t>수집가의 가방</t>
+          <t>도굴꾼 장갑</t>
         </is>
       </c>
       <c r="C118" s="4" t="inlineStr">
         <is>
-          <t>Collector's Bag</t>
+          <t>Grave Robber's Gloves</t>
         </is>
       </c>
       <c r="D118" s="5" t="inlineStr">
@@ -7204,24 +6851,24 @@
       </c>
       <c r="N118" s="4" t="inlineStr">
         <is>
-          <t>획득 즉시 보유 중인 다른 유물 1개의 효과를 복사한다</t>
+          <t>보물상자의 보상 선택지가 1개 늘어난다</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="4" t="inlineStr">
         <is>
-          <t>relic_grave_robbers_gloves</t>
+          <t>relic_finishing_blow</t>
         </is>
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>도굴꾼 장갑</t>
+          <t>최후의 일격</t>
         </is>
       </c>
       <c r="C119" s="4" t="inlineStr">
         <is>
-          <t>Grave Robber's Gloves</t>
+          <t>Finishing Blow</t>
         </is>
       </c>
       <c r="D119" s="5" t="inlineStr">
@@ -7258,61 +6905,514 @@
       </c>
       <c r="N119" s="4" t="inlineStr">
         <is>
-          <t>보물상자의 보상 선택지가 1개 늘어난다</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="4" t="inlineStr">
-        <is>
-          <t>relic_finishing_blow</t>
-        </is>
-      </c>
-      <c r="B120" s="4" t="inlineStr">
-        <is>
-          <t>최후의 일격</t>
-        </is>
-      </c>
-      <c r="C120" s="4" t="inlineStr">
-        <is>
-          <t>Finishing Blow</t>
-        </is>
-      </c>
-      <c r="D120" s="5" t="inlineStr">
-        <is>
-          <t>Common</t>
-        </is>
-      </c>
-      <c r="E120" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F120" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G120" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H120" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I120" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J120" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K120" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L120" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M120" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N120" s="4" t="inlineStr">
-        <is>
           <t>상대의 체력 비율이 내 체력 비율보다 낮을 때 피해 2배 (전투당 1회)</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="29" t="inlineStr">
+        <is>
+          <t>[시작 유물 - 캐릭터 전용 (StartingRelicData, 일반 유물과 별개 시스템)]</t>
+        </is>
+      </c>
+      <c r="B121" s="29" t="n"/>
+      <c r="C121" s="29" t="n"/>
+      <c r="D121" s="29" t="n"/>
+      <c r="E121" s="29" t="n"/>
+      <c r="F121" s="29" t="n"/>
+      <c r="G121" s="29" t="n"/>
+      <c r="H121" s="29" t="n"/>
+      <c r="I121" s="29" t="n"/>
+      <c r="J121" s="29" t="n"/>
+      <c r="K121" s="29" t="n"/>
+      <c r="L121" s="29" t="n"/>
+      <c r="M121" s="29" t="n"/>
+      <c r="N121" s="29" t="n"/>
+      <c r="O121" s="29" t="n"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="4" t="inlineStr">
+        <is>
+          <t>startingrelic_oldcompass</t>
+        </is>
+      </c>
+      <c r="B122" s="4" t="inlineStr">
+        <is>
+          <t>낡은 나침반</t>
+        </is>
+      </c>
+      <c r="C122" s="4" t="inlineStr">
+        <is>
+          <t>Old Compass</t>
+        </is>
+      </c>
+      <c r="D122" s="4" t="inlineStr">
+        <is>
+          <t>StartingRelic</t>
+        </is>
+      </c>
+      <c r="E122" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F122" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G122" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H122" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I122" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J122" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K122" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L122" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M122" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N122" s="4" t="inlineStr">
+        <is>
+          <t>Event 노드 등장 확률 소폭 증가 (EventChoiceRollBonus +0.1)</t>
+        </is>
+      </c>
+      <c r="O122" s="4" t="inlineStr">
+        <is>
+          <t>소유 캐릭터: 모험가(Adventurer)</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="4" t="inlineStr">
+        <is>
+          <t>startingrelic_hammer</t>
+        </is>
+      </c>
+      <c r="B123" s="4" t="inlineStr">
+        <is>
+          <t>망치</t>
+        </is>
+      </c>
+      <c r="C123" s="4" t="inlineStr">
+        <is>
+          <t>Hammer</t>
+        </is>
+      </c>
+      <c r="D123" s="4" t="inlineStr">
+        <is>
+          <t>StartingRelic</t>
+        </is>
+      </c>
+      <c r="E123" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F123" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G123" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H123" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I123" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J123" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K123" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L123" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M123" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N123" s="4" t="inlineStr">
+        <is>
+          <t>곡괭이 내구도 감소량 추가 감소 (PickaxeDurabilityReduction 0.2)</t>
+        </is>
+      </c>
+      <c r="O123" s="4" t="inlineStr">
+        <is>
+          <t>소유 캐릭터: 대장장이(Blacksmith)</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="4" t="inlineStr">
+        <is>
+          <t>startingrelic_smallvial</t>
+        </is>
+      </c>
+      <c r="B124" s="4" t="inlineStr">
+        <is>
+          <t>작은 약병</t>
+        </is>
+      </c>
+      <c r="C124" s="4" t="inlineStr">
+        <is>
+          <t>Small Vial</t>
+        </is>
+      </c>
+      <c r="D124" s="4" t="inlineStr">
+        <is>
+          <t>StartingRelic</t>
+        </is>
+      </c>
+      <c r="E124" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F124" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G124" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H124" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I124" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J124" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K124" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L124" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M124" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N124" s="4" t="inlineStr">
+        <is>
+          <t>포션 회복량 추가 증가 (PotionHealBonus +0.1)</t>
+        </is>
+      </c>
+      <c r="O124" s="4" t="inlineStr">
+        <is>
+          <t>소유 캐릭터: 연금술사(Alchemist)</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="4" t="inlineStr">
+        <is>
+          <t>startingrelic_luckycoin</t>
+        </is>
+      </c>
+      <c r="B125" s="4" t="inlineStr">
+        <is>
+          <t>행운의 동전</t>
+        </is>
+      </c>
+      <c r="C125" s="4" t="inlineStr">
+        <is>
+          <t>Lucky Coin</t>
+        </is>
+      </c>
+      <c r="D125" s="4" t="inlineStr">
+        <is>
+          <t>StartingRelic</t>
+        </is>
+      </c>
+      <c r="E125" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F125" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G125" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H125" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I125" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J125" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K125" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L125" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M125" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N125" s="4" t="inlineStr">
+        <is>
+          <t>보물상자에서 유물 등장 확률 추가 증가 (TreasureRewardBonus +0.01)</t>
+        </is>
+      </c>
+      <c r="O125" s="4" t="inlineStr">
+        <is>
+          <t>소유 캐릭터: 보물사냥꾼(TreasureHunter)</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="4" t="inlineStr">
+        <is>
+          <t>startingrelic_holywater</t>
+        </is>
+      </c>
+      <c r="B126" s="4" t="inlineStr">
+        <is>
+          <t>축복의 성수</t>
+        </is>
+      </c>
+      <c r="C126" s="4" t="inlineStr">
+        <is>
+          <t>Blessed Water</t>
+        </is>
+      </c>
+      <c r="D126" s="4" t="inlineStr">
+        <is>
+          <t>StartingRelic</t>
+        </is>
+      </c>
+      <c r="E126" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F126" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G126" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H126" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I126" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J126" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K126" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L126" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M126" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N126" s="4" t="inlineStr">
+        <is>
+          <t>저주형 디버프 지속시간 추가 감소 (CurseDurationReduction 0.1)</t>
+        </is>
+      </c>
+      <c r="O126" s="4" t="inlineStr">
+        <is>
+          <t>소유 캐릭터: 신앙기사(Priest)</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="4" t="inlineStr">
+        <is>
+          <t>startingrelic_bloodpendant</t>
+        </is>
+      </c>
+      <c r="B127" s="4" t="inlineStr">
+        <is>
+          <t>핏빛 펜던트</t>
+        </is>
+      </c>
+      <c r="C127" s="4" t="inlineStr">
+        <is>
+          <t>Blood Pendant</t>
+        </is>
+      </c>
+      <c r="D127" s="4" t="inlineStr">
+        <is>
+          <t>StartingRelic</t>
+        </is>
+      </c>
+      <c r="E127" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F127" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G127" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H127" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I127" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J127" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K127" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L127" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M127" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N127" s="4" t="inlineStr">
+        <is>
+          <t>체력 30% 이하일 때 추가 공격력 (LowHpAttackBonus +0.05)</t>
+        </is>
+      </c>
+      <c r="O127" s="4" t="inlineStr">
+        <is>
+          <t>소유 캐릭터: 광전사(Berserker)</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="4" t="inlineStr">
+        <is>
+          <t>startingrelic_minergloves</t>
+        </is>
+      </c>
+      <c r="B128" s="4" t="inlineStr">
+        <is>
+          <t>광부 장갑</t>
+        </is>
+      </c>
+      <c r="C128" s="4" t="inlineStr">
+        <is>
+          <t>Miner's Gloves</t>
+        </is>
+      </c>
+      <c r="D128" s="4" t="inlineStr">
+        <is>
+          <t>StartingRelic</t>
+        </is>
+      </c>
+      <c r="E128" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F128" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G128" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H128" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I128" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J128" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K128" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L128" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M128" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N128" s="4" t="inlineStr">
+        <is>
+          <t>광물 획득량 소폭 증가 (MiningGainBonus +0.01)</t>
+        </is>
+      </c>
+      <c r="O128" s="4" t="inlineStr">
+        <is>
+          <t>소유 캐릭터: 광부(Miner)</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="4" t="inlineStr">
+        <is>
+          <t>startingrelic_rustysword</t>
+        </is>
+      </c>
+      <c r="B129" s="4" t="inlineStr">
+        <is>
+          <t>녹슨 검</t>
+        </is>
+      </c>
+      <c r="C129" s="4" t="inlineStr">
+        <is>
+          <t>Rusty Sword</t>
+        </is>
+      </c>
+      <c r="D129" s="4" t="inlineStr">
+        <is>
+          <t>StartingRelic</t>
+        </is>
+      </c>
+      <c r="E129" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F129" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G129" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H129" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I129" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J129" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K129" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L129" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M129" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N129" s="4" t="inlineStr">
+        <is>
+          <t>고정 공격력 보너스 (FixedAttackBonus +1)</t>
+        </is>
+      </c>
+      <c r="O129" s="4" t="inlineStr">
+        <is>
+          <t>소유 캐릭터: 용병(Mercenary)</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="4" t="inlineStr">
+        <is>
+          <t>※ 죄인(Prisoner), 도굴꾼(GraveRobber)은 시작 유물이 배정되어 있지 않음(StartingRelic: None).</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="4" t="inlineStr">
+        <is>
+          <t>※ 유물 신규 효과 시스템 안내: 최근 추가된 유물 다수는 개별 수치 컬럼(공격력~곡괭이내구도) 대신 effects 리스트 기반 신규 시스템을 사용합니다. 해당 컬럼이 전부 0인 항목은 "효과 요약" 컬럼을 참고하세요.</t>
         </is>
       </c>
     </row>
@@ -7327,7 +7427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:H32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="12.75"/>
   <cols>
     <col width="18" customWidth="1" style="21" min="1" max="1"/>
@@ -7335,6 +7435,7 @@
     <col width="12" customWidth="1" style="21" min="4" max="5"/>
     <col width="10" customWidth="1" style="21" min="6" max="6"/>
     <col width="36" customWidth="1" style="21" min="7" max="7"/>
+    <col width="40" customWidth="1" style="21" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="18" customHeight="1" s="21">
@@ -7371,6 +7472,11 @@
       <c r="G1" s="2" t="inlineStr">
         <is>
           <t>설명</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>비고</t>
         </is>
       </c>
     </row>
@@ -7610,115 +7716,115 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="n"/>
-      <c r="B9" s="6" t="n"/>
-      <c r="C9" s="6" t="n"/>
-      <c r="D9" s="6" t="n"/>
-      <c r="E9" s="6" t="n"/>
-      <c r="F9" s="6" t="n"/>
-      <c r="G9" s="6" t="n"/>
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Item_Dirt</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>흙</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Dirt</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>Resource</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>채굴 시 획득. BlockType.Dirt 대응 자원. 현재 판매/용도 없음</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>[소모품]</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="n"/>
-      <c r="C10" s="3" t="n"/>
-      <c r="D10" s="3" t="n"/>
-      <c r="E10" s="3" t="n"/>
-      <c r="F10" s="3" t="n"/>
-      <c r="G10" s="3" t="n"/>
+      <c r="A10" s="6" t="n"/>
+      <c r="B10" s="6" t="n"/>
+      <c r="C10" s="6" t="n"/>
+      <c r="D10" s="6" t="n"/>
+      <c r="E10" s="6" t="n"/>
+      <c r="F10" s="6" t="n"/>
+      <c r="G10" s="6" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
+          <t>[소모품]</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n"/>
+      <c r="C11" s="3" t="n"/>
+      <c r="D11" s="3" t="n"/>
+      <c r="E11" s="3" t="n"/>
+      <c r="F11" s="3" t="n"/>
+      <c r="G11" s="3" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
           <t>Item_BurnCure</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>화상 치료제</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>Burn Cure</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>Consumable</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="E12" s="3" t="inlineStr">
         <is>
           <t>Common</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="F12" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="G12" s="3" t="inlineStr">
         <is>
           <t>인벤토리에서 사용 시 화상 상태 즉시 해제</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>Item_Potion</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>회복약</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>Health Potion</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>Consumable</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>Common</t>
-        </is>
-      </c>
-      <c r="F12" s="5" t="inlineStr">
-        <is>
-          <t>+5 HP</t>
-        </is>
-      </c>
-      <c r="G12" s="4" t="inlineStr">
-        <is>
-          <t>인벤토리에서 사용 시 체력 5 회복</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Item_Potion_Medium</t>
+          <t>Item_Potion</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>회복약(중)</t>
+          <t>회복약</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Health Potion (Medium)</t>
+          <t>Health Potion</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
@@ -7733,29 +7839,29 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>+10 HP</t>
+          <t>+5 HP</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>인벤토리에서 사용 시 체력 10 회복</t>
+          <t>인벤토리에서 사용 시 체력 5 회복</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Item_Potion_Large</t>
+          <t>Item_Potion_Medium</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>회복약(대)</t>
+          <t>회복약(중)</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Health Potion (Large)</t>
+          <t>Health Potion (Medium)</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
@@ -7770,29 +7876,29 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>+20 HP</t>
+          <t>+10 HP</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>인벤토리에서 사용 시 체력 20 회복</t>
+          <t>인벤토리에서 사용 시 체력 10 회복</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Item_Key</t>
+          <t>Item_Potion_Large</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>열쇠</t>
+          <t>회복약(대)</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Chest Key</t>
+          <t>Health Potion (Large)</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
@@ -7802,34 +7908,34 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t>Common</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+20 HP</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>잠긴 보물상자 개방에 사용 (현재 미구현)</t>
+          <t>인벤토리에서 사용 시 체력 20 회복</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Item_Chest</t>
+          <t>Item_Key</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>보물상자</t>
+          <t>열쇠</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Treasure Box</t>
+          <t>Chest Key</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
@@ -7839,7 +7945,7 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>Epic</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
@@ -7849,24 +7955,24 @@
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>사용 시 랜덤 보상 획득</t>
+          <t>잠긴 보물상자 개방에 사용 (현재 미구현)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Item_Special</t>
+          <t>Item_Chest</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>특수 소모품</t>
+          <t>보물상자</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Elixir</t>
+          <t>Treasure Box</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
@@ -7876,34 +7982,34 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>Legendary</t>
+          <t>Epic</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>+10 HP</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>사용 시 체력 10 회복</t>
+          <t>사용 시 랜덤 보상 획득</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>Item_PortableAnvil</t>
+          <t>Item_Special</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>간이 모루</t>
+          <t>특수 소모품</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>Portable Anvil</t>
+          <t>Elixir</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
@@ -7913,108 +8019,108 @@
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t>Legendary</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>+5 내구도</t>
+          <t>+10 HP</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>인벤토리에서 사용 시 곡괭이 내구도 5 회복 (최대치 초과 불가)</t>
+          <t>사용 시 체력 10 회복</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
+          <t>Item_PortableAnvil</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>간이 모루</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>Portable Anvil</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>Consumable</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>+5 내구도</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>인벤토리에서 사용 시 곡괭이 내구도 5 회복 (최대치 초과 불가)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
           <t>Item_ImmortalityPotion</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>불사 물약</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>Potion of Immortality</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="D20" s="5" t="inlineStr">
         <is>
           <t>Consumable</t>
         </is>
       </c>
-      <c r="E19" s="5" t="inlineStr">
+      <c r="E20" s="5" t="inlineStr">
         <is>
           <t>Legendary</t>
         </is>
       </c>
-      <c r="F19" s="5" t="inlineStr">
+      <c r="F20" s="5" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G19" s="4" t="inlineStr">
+      <c r="G20" s="4" t="inlineStr">
         <is>
           <t>사망 시 자동 소비되어 체력 5로 부활 (1회 한정, 수동 사용 불가)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Item_RepairKit</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>수리 키트</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Repair Kit</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Consumable</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Common</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>+3 내구도</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>인벤토리에서 사용 시 곡괭이 내구도 3 회복</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Item_AntidotePotion</t>
+          <t>Item_RepairKit</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>해독제</t>
+          <t>수리 키트</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Antidote</t>
+          <t>Repair Kit</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -8029,29 +8135,29 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+3 내구도</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>인벤토리에서 사용 시 중독 상태 즉시 해제</t>
+          <t>인벤토리에서 사용 시 곡괭이 내구도 3 회복</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Item_Bomb</t>
+          <t>Item_AntidotePotion</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>폭탄</t>
+          <t>해독제</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Bomb</t>
+          <t>Antidote</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -8066,29 +8172,29 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>5 피해</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>전투 중인 몬스터 전체에게 5의 피해. 전투 중에만 사용 가능</t>
+          <t>인벤토리에서 사용 시 중독 상태 즉시 해제</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Item_HolyWater</t>
+          <t>Item_Bomb</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>정화의 성수</t>
+          <t>폭탄</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Holy Water</t>
+          <t>Bomb</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -8098,34 +8204,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t>Common</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>5 피해</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>인벤토리에서 사용 시 화상+중독 상태 동시 해제</t>
+          <t>전투 중인 몬스터 전체에게 5의 피해. 전투 중에만 사용 가능</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Item_EnhancedRepairKit</t>
+          <t>Item_HolyWater</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>강화 수리 키트</t>
+          <t>정화의 성수</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Enhanced Repair Kit</t>
+          <t>Holy Water</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -8140,29 +8246,29 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>+10 내구도</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>인벤토리에서 사용 시 곡괭이 내구도 10 회복</t>
+          <t>인벤토리에서 사용 시 화상+중독 상태 동시 해제</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Item_EnhancedBomb</t>
+          <t>Item_EnhancedRepairKit</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>강화 폭탄</t>
+          <t>강화 수리 키트</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Enhanced Bomb</t>
+          <t>Enhanced Repair Kit</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -8177,29 +8283,29 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>15 피해</t>
+          <t>+10 내구도</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>전투 중인 몬스터 전체에게 15의 피해. 전투 중에만 사용 가능</t>
+          <t>인벤토리에서 사용 시 곡괭이 내구도 10 회복</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Item_AngelFeather</t>
+          <t>Item_EnhancedBomb</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>천사의 깃털</t>
+          <t>강화 폭탄</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Angel Feather</t>
+          <t>Enhanced Bomb</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -8209,34 +8315,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Legendary</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>풀 HP 회복</t>
+          <t>15 피해</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>체력 완전 회복 + 화상/중독 동시 치료</t>
+          <t>전투 중인 몬스터 전체에게 15의 피해. 전투 중에만 사용 가능</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Item_FullRepairKit</t>
+          <t>Item_AngelFeather</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>완전 수리 키트</t>
+          <t>천사의 깃털</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Full Repair Kit</t>
+          <t>Angel Feather</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -8251,49 +8357,136 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>풀 내구도</t>
+          <t>풀 HP 회복</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>곡괭이 내구도 완전 회복</t>
+          <t>체력 완전 회복 + 화상/중독 동시 치료</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>Item_FullRepairKit</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>완전 수리 키트</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Full Repair Kit</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Consumable</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Legendary</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>풀 내구도</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>곡괭이 내구도 완전 회복</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>Item_GuardianHeart</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>수호자의 심장</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>Guardian's Heart</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>Consumable</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>Legendary</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>사망 시 자동 소비되어 체력 15로 부활 (1회 한정, 수동 사용 불가)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>[기타 - 시작 소지품 전용]</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n"/>
+      <c r="C31" s="3" t="n"/>
+      <c r="D31" s="3" t="n"/>
+      <c r="E31" s="3" t="n"/>
+      <c r="F31" s="3" t="n"/>
+      <c r="G31" s="3" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Item_Torch</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>횃불</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Torch</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Resource</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>모험가(Adventurer) 시작 소지품 전용. 기능적 효과 없음(장식용)</t>
         </is>
       </c>
     </row>
@@ -8308,13 +8501,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="12.75"/>
   <cols>
     <col width="12" customWidth="1" style="21" min="1" max="3"/>
     <col width="10" customWidth="1" style="21" min="4" max="4"/>
     <col width="40" customWidth="1" style="21" min="5" max="5"/>
     <col width="14" customWidth="1" style="21" min="6" max="10"/>
+    <col width="40" customWidth="1" style="21" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1" s="21">
@@ -8368,6 +8562,11 @@
           <t>D250+</t>
         </is>
       </c>
+      <c r="K1" s="2" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
@@ -8418,6 +8617,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>Item_Dirt(아이템 시트)로 인벤토리에 적재됨. 판매/구매 용도 없음</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
@@ -8518,6 +8722,11 @@
           <t>10%</t>
         </is>
       </c>
+      <c r="K4" s="5" t="inlineStr">
+        <is>
+          <t>파괴 시 40% 확률로 체력 +2 즉시 회복(별도 즉시효과, 인벤토리 적재 아님)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
@@ -8568,6 +8777,11 @@
           <t>20%</t>
         </is>
       </c>
+      <c r="K5" s="5" t="inlineStr">
+        <is>
+          <t>곡괭이 수리 및 상점 구매(Will 환산 정산)에 사용</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -8618,6 +8832,11 @@
           <t>20%</t>
         </is>
       </c>
+      <c r="K6" s="5" t="inlineStr">
+        <is>
+          <t>상점 구매(Will 환산 정산)에 사용</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -8668,6 +8887,11 @@
           <t>20%</t>
         </is>
       </c>
+      <c r="K7" s="5" t="inlineStr">
+        <is>
+          <t>상점 구매(Will 환산 정산)에 사용</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -8716,6 +8940,11 @@
       <c r="J8" s="5" t="inlineStr">
         <is>
           <t>10%</t>
+        </is>
+      </c>
+      <c r="K8" s="5" t="inlineStr">
+        <is>
+          <t>최상급 곡괭이 구매(Will 환산 정산)에 사용</t>
         </is>
       </c>
     </row>
@@ -8762,7 +8991,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="12.75"/>
   <cols>
     <col width="20" customWidth="1" style="21" min="1" max="1"/>
@@ -8771,6 +9000,7 @@
     <col width="14" customWidth="1" style="21" min="5" max="5"/>
     <col width="16" customWidth="1" style="21" min="6" max="7"/>
     <col width="28" customWidth="1" style="21" min="8" max="8"/>
+    <col width="45" customWidth="1" style="21" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="18" customHeight="1" s="21">
@@ -8814,6 +9044,11 @@
           <t>구매 비용</t>
         </is>
       </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
@@ -8887,7 +9122,12 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>철 ×50</t>
+          <t>Will 50</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>가격 산정 방식이 광석 조합 → Will 단일 재화로 변경됨(과거 시트 값은 최신 코드와 불일치하여 수정)</t>
         </is>
       </c>
     </row>
@@ -8925,7 +9165,12 @@
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>철 ×100, 은 ×50</t>
+          <t>Will 250</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>가격 산정 방식이 광석 조합 → Will 단일 재화로 변경됨(과거 시트 값은 최신 코드와 불일치하여 수정)</t>
         </is>
       </c>
     </row>
@@ -8963,7 +9208,12 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>은 ×100, 금 ×30</t>
+          <t>Will 380</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>가격 산정 방식이 광석 조합 → Will 단일 재화로 변경됨(과거 시트 값은 최신 코드와 불일치하여 수정)</t>
         </is>
       </c>
     </row>
@@ -9001,19 +9251,435 @@
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>금 ×50, 다이아 ×20</t>
+          <t>Will 550</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>가격 산정 방식이 광석 조합 → Will 단일 재화로 변경됨(과거 시트 값은 최신 코드와 불일치하여 수정)</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="inlineStr">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>※ Pickaxe_Default.asset은 Addressables 미등록 상태로 실제 상점에 노출되지 않는 고아 애셋(목록에서 제외)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>※ 수리효율</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B9" s="8" t="inlineStr">
         <is>
           <t>내구도 1 회복 시 소모 재료 배율. 1.0x = 재료 1개당 내구도 1 회복</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="29" t="inlineStr">
+        <is>
+          <t>[캐릭터]</t>
+        </is>
+      </c>
+      <c r="B11" s="29" t="n"/>
+      <c r="C11" s="29" t="n"/>
+      <c r="D11" s="29" t="n"/>
+      <c r="E11" s="29" t="n"/>
+      <c r="F11" s="29" t="n"/>
+      <c r="G11" s="29" t="n"/>
+      <c r="H11" s="29" t="n"/>
+      <c r="I11" s="29" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>캐릭터ID</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>이름(KO)</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>이름(EN)</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>패시브 요약</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="n"/>
+      <c r="F12" s="2" t="n"/>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>기본보유</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>해금 비용</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Prisoner</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>죄인</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Prisoner</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>특별한 고유 능력 없음(기준 캐릭터)</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="n"/>
+      <c r="F13" s="5" t="n"/>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>O (기본)</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>무료</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Mercenary</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>용병</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Mercenary</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>공격력 +1</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="n"/>
+      <c r="F14" s="5" t="n"/>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>Will 60</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Miner</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>광부</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>Miner</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>채굴력 +1</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" s="5" t="n"/>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>Will 90</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>GraveRobber</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>도굴꾼</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Grave Robber</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>철/은/금/다이아 획득 시 10% 확률로 10% 추가 획득</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="n"/>
+      <c r="F16" s="5" t="n"/>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>Will 150</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>가격을 자동 산식이 아닌 수동으로 150 지정(정성적 티어 기준)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Adventurer</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>모험가</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>Adventurer</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>확률로 이벤트 노드 보너스 선택지 등장</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="n"/>
+      <c r="F17" s="5" t="n"/>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>Will 60</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Blacksmith</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>대장장이</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>Blacksmith</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>곡괭이 내구도 감소량 감소</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="n"/>
+      <c r="F18" s="5" t="n"/>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>Will 130</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Alchemist</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>연금술사</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>Alchemist</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>포션 회복량 증가</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="n"/>
+      <c r="F19" s="5" t="n"/>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>Will 60</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>TreasureHunter</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>보물사냥꾼</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>Treasure Hunter</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>보물상자 보상 개수 +1, 유물 등장 확률 증가</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="n"/>
+      <c r="F20" s="5" t="n"/>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>구매 불가</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="inlineStr">
+        <is>
+          <t>PurchasableInShop=false — 업적 'ach_depth200(지하 심층)' 달성 시에만 무료 해금. 가격 자리에 해금 조건 문구 표시</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Priest</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>신앙기사</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>Priest</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>저주형 디버프 지속시간 감소</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="n"/>
+      <c r="F21" s="5" t="n"/>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>Will 90</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Berserker</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>광전사</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>Berserker</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>체력이 낮을수록 공격력 증가</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="n"/>
+      <c r="F22" s="5" t="n"/>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>Will 180</t>
         </is>
       </c>
     </row>
@@ -9028,7 +9694,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="22" customWidth="1" style="21" min="1" max="1"/>
@@ -9039,6 +9705,7 @@
     <col width="16" customWidth="1" style="21" min="6" max="6"/>
     <col width="10" customWidth="1" style="21" min="7" max="7"/>
     <col width="36" customWidth="1" style="21" min="8" max="8"/>
+    <col width="50" customWidth="1" style="21" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="18" customHeight="1" s="21">
@@ -9082,6 +9749,11 @@
           <t>설명(KO)</t>
         </is>
       </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="12.75" customHeight="1" s="21">
       <c r="A2" s="4" t="inlineStr">
@@ -9242,6 +9914,11 @@
           <t>깊이 200에 도달합니다.</t>
         </is>
       </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>달성 시 보상으로 보물사냥꾼(TreasureHunter) 캐릭터 무료 해금 예정 (Will 보상안과 함께 논의 중, 보상 지급 코드는 아직 미구현)</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="12.75" customHeight="1" s="21">
       <c r="A6" s="4" t="inlineStr">
@@ -9282,6 +9959,11 @@
           <t>몬스터 10마리를 처치합니다.</t>
         </is>
       </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>일반 몬스터 처치만 집계 — 엘리트/보스 처치는 미포함(EliteCombatSystem/BossManager는 FireMonsterKilled 미호출)</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="12.75" customHeight="1" s="21">
       <c r="A7" s="4" t="inlineStr">
@@ -9322,6 +10004,11 @@
           <t>몬스터 50마리를 처치합니다.</t>
         </is>
       </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>일반 몬스터 처치만 집계 — 엘리트/보스 처치는 미포함(EliteCombatSystem/BossManager는 FireMonsterKilled 미호출)</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="12.75" customHeight="1" s="21">
       <c r="A8" s="4" t="inlineStr">
@@ -9720,6 +10407,27 @@
       <c r="H17" s="4" t="inlineStr">
         <is>
           <t>보물 상자를 5개 엽니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>※ [점검 이력] 완료 알림(토스트)이 2번째 런부터 표시되지 않는 버그 발견 — AchievementNotificationView가 GameManager.InitializeUIAsync() 재호출 시마다 새로 생성/구독되며 이전 구독을 해제하지 않던 문제. 구독 해제 로직 추가 + Addressables 프리팹화 + Coroutine→UniTask 전환으로 수정 완료(실측 검증됨).</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>※ [보상 시스템] AchievementData.rewardType/rewardValue 필드는 존재하나, 실제로 보상을 지급하는 코드는 프로젝트 전체에 없음(현재 전 항목 rewardType=None). Will 보상안(전체 약 293) + ach_depth200 캐릭터 보상안을 제안했으며 구현은 미확정.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>※ [미사용 타입] AchievementType 15종 중 RepairWithOre/UnlockCharacter/TombstoneOpen/WaterEncounter/Custom 5종은 이벤트 처리 코드는 있으나 이를 사용하는 업적 자산이 없음. 그중 Custom은 업데이트 로직 자체가 없어 실제로 배정하면 영구히 진행되지 않음.</t>
         </is>
       </c>
     </row>
@@ -9734,7 +10442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P14"/>
+  <dimension ref="A1:Q15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="12.75"/>
   <cols>
     <col width="30" customWidth="1" style="21" min="1" max="1"/>
@@ -9750,6 +10458,7 @@
     <col width="12" customWidth="1" style="21" min="13" max="14"/>
     <col width="14" customWidth="1" style="21" min="15" max="15"/>
     <col width="12" customWidth="1" style="21" min="16" max="16"/>
+    <col width="55" customWidth="1" style="21" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1" s="21">
@@ -9831,6 +10540,11 @@
       <c r="P1" s="9" t="inlineStr">
         <is>
           <t>D200+ 가중치</t>
+        </is>
+      </c>
+      <c r="Q1" s="9" t="inlineStr">
+        <is>
+          <t>비고</t>
         </is>
       </c>
     </row>
@@ -10338,6 +11052,13 @@
       <c r="A14" s="20" t="inlineStr">
         <is>
           <t>※ 가중치 '-' = 해당 구간 미출현</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="20" t="inlineStr">
+        <is>
+          <t>※ 이 시트는 MonsterSpawnTable(일반 몬스터) 기준입니다. 엘리트 몬스터 6종(BigSlime/CursedKnight/CursedPriest/IronPlateSpider/MerchantMimic/SkeletonMiner, EliteSpawnTable 등록)과 보스 5종은 별도 시스템(EliteCombatSystem/BossManager)으로 관리되며 이 시트에는 포함되지 않습니다.</t>
         </is>
       </c>
     </row>
@@ -10359,7 +11080,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="12.75"/>
   <cols>
     <col width="16" customWidth="1" style="21" min="1" max="1"/>
@@ -10368,6 +11089,7 @@
     <col width="14" customWidth="1" style="21" min="5" max="5"/>
     <col width="26" customWidth="1" style="21" min="6" max="6"/>
     <col width="48" customWidth="1" style="21" min="7" max="7"/>
+    <col width="55" customWidth="1" style="21" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.95" customHeight="1" s="21">
@@ -10404,6 +11126,11 @@
       <c r="G1" s="9" t="inlineStr">
         <is>
           <t>설명</t>
+        </is>
+      </c>
+      <c r="H1" s="9" t="inlineStr">
+        <is>
+          <t>비고</t>
         </is>
       </c>
     </row>
@@ -10723,99 +11450,118 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="63.75" customHeight="1" s="21">
-      <c r="A13" s="22" t="inlineStr">
-        <is>
-          <t>[맵 생성 파라미터 (MapGenerationConfig ScriptableObject)]</t>
-        </is>
-      </c>
-      <c r="B13" s="23" t="n"/>
-      <c r="C13" s="23" t="n"/>
-      <c r="D13" s="23" t="n"/>
-      <c r="E13" s="23" t="n"/>
-      <c r="F13" s="23" t="n"/>
-      <c r="G13" s="24" t="n"/>
-    </row>
+    <row r="12">
+      <c r="A12" s="25" t="inlineStr">
+        <is>
+          <t>Start</t>
+        </is>
+      </c>
+      <c r="B12" s="25" t="inlineStr">
+        <is>
+          <t>광산 입구</t>
+        </is>
+      </c>
+      <c r="C12" s="25" t="inlineStr">
+        <is>
+          <t>Mine Entrance</t>
+        </is>
+      </c>
+      <c r="D12" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E12" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="25" t="inlineStr">
+        <is>
+          <t>NodeIconData.Start 항목</t>
+        </is>
+      </c>
+      <c r="G12" s="25" t="inlineStr">
+        <is>
+          <t>각 50층 구간의 시작점(채굴 시작 노드). EntranceConnector가 RoomType.Start로 고정 배정, 가중치 랜덤 배정 대상 아님.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="63.75" customHeight="1" s="21"/>
     <row r="14" ht="25.5" customHeight="1" s="21">
-      <c r="A14" s="26" t="inlineStr">
+      <c r="A14" s="22" t="inlineStr">
+        <is>
+          <t>[맵 생성 파라미터 (RoomGenerationConfig ScriptableObject)]</t>
+        </is>
+      </c>
+      <c r="B14" s="23" t="n"/>
+      <c r="C14" s="23" t="n"/>
+      <c r="D14" s="23" t="n"/>
+      <c r="E14" s="23" t="n"/>
+      <c r="F14" s="23" t="n"/>
+      <c r="G14" s="24" t="n"/>
+    </row>
+    <row r="15" ht="25.5" customHeight="1" s="21">
+      <c r="A15" s="26" t="inlineStr">
         <is>
           <t>NodesPerMap</t>
         </is>
       </c>
-      <c r="B14" s="26" t="inlineStr">
+      <c r="B15" s="26" t="inlineStr">
         <is>
           <t>맵당 노드 수 (Depth 수)</t>
         </is>
       </c>
-      <c r="C14" s="14" t="inlineStr">
+      <c r="C15" s="14" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="D14" s="14" t="n"/>
-      <c r="E14" s="14" t="n"/>
-      <c r="F14" s="14" t="n"/>
-      <c r="G14" s="14" t="n"/>
-    </row>
-    <row r="15" ht="25.5" customHeight="1" s="21">
-      <c r="A15" s="25" t="inlineStr">
+      <c r="D15" s="14" t="n"/>
+      <c r="E15" s="14" t="n"/>
+      <c r="F15" s="14" t="n"/>
+      <c r="G15" s="14" t="n"/>
+    </row>
+    <row r="16" ht="25.5" customHeight="1" s="21">
+      <c r="A16" s="25" t="inlineStr">
         <is>
           <t>MinBranches</t>
         </is>
       </c>
-      <c r="B15" s="25" t="inlineStr">
+      <c r="B16" s="25" t="inlineStr">
         <is>
           <t>레이어당 최소 분기</t>
         </is>
       </c>
-      <c r="C15" s="16" t="inlineStr">
+      <c r="C16" s="16" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D15" s="16" t="n"/>
-      <c r="E15" s="16" t="n"/>
-      <c r="F15" s="16" t="n"/>
-      <c r="G15" s="16" t="n"/>
-    </row>
-    <row r="16" ht="25.5" customHeight="1" s="21">
-      <c r="A16" s="26" t="inlineStr">
+      <c r="D16" s="16" t="n"/>
+      <c r="E16" s="16" t="n"/>
+      <c r="F16" s="16" t="n"/>
+      <c r="G16" s="16" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="26" t="inlineStr">
         <is>
           <t>MaxBranches</t>
         </is>
       </c>
-      <c r="B16" s="26" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>레이어당 최대 분기</t>
         </is>
       </c>
-      <c r="C16" s="14" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D16" s="14" t="n"/>
-      <c r="E16" s="14" t="n"/>
-      <c r="F16" s="14" t="n"/>
-      <c r="G16" s="14" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="25" t="inlineStr">
+    </row>
+    <row r="18">
+      <c r="A18" s="25" t="inlineStr">
         <is>
           <t>Depth 1</t>
-        </is>
-      </c>
-      <c r="B17" s="23" t="n"/>
-      <c r="C17" s="23" t="n"/>
-      <c r="D17" s="23" t="n"/>
-      <c r="E17" s="23" t="n"/>
-      <c r="F17" s="23" t="n"/>
-      <c r="G17" s="24" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="26" t="inlineStr">
-        <is>
-          <t>Depth 50</t>
         </is>
       </c>
       <c r="B18" s="23" t="n"/>
@@ -10825,42 +11571,67 @@
       <c r="F18" s="23" t="n"/>
       <c r="G18" s="24" t="n"/>
     </row>
-    <row r="19"/>
-    <row r="20">
-      <c r="A20" s="20" t="inlineStr">
-        <is>
-          <t>※ 가중치는 MapGenerationConfig.NodeWeights 리스트에서 관리. Boss는 항상 고정이므로 가중치 없음.</t>
-        </is>
-      </c>
-    </row>
+    <row r="19">
+      <c r="A19" s="26" t="inlineStr">
+        <is>
+          <t>Depth 50</t>
+        </is>
+      </c>
+      <c r="B19" s="23" t="n"/>
+      <c r="C19" s="23" t="n"/>
+      <c r="D19" s="23" t="n"/>
+      <c r="E19" s="23" t="n"/>
+      <c r="F19" s="23" t="n"/>
+      <c r="G19" s="24" t="n"/>
+    </row>
+    <row r="20"/>
     <row r="21" ht="48" customHeight="1" s="21">
       <c r="A21" s="20" t="inlineStr">
         <is>
-          <t>※ 모든 경로는 Boss(Depth50)에서 합류. 막힌 경로(Dead End) 없음.</t>
+          <t>※ 가중치는 RoomGenerationConfig._weights 리스트에서 관리. Boss는 항상 고정이므로 가중치 없음.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="84" customHeight="1" s="21">
       <c r="A22" s="20" t="inlineStr">
         <is>
-          <t>※ UI: UI_Panel_MapPopup Prefab (Addressable). 노드 = Map_Node, 연결선 = Map_Line Prefab.</t>
+          <t>※ 모든 경로는 Boss(Depth50)에서 합류. 막힌 경로(Dead End) 없음.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="96" customHeight="1" s="21">
       <c r="A23" s="20" t="inlineStr">
         <is>
-          <t>※ Addressable Key: Map_GenerationConfig (MapGenerationConfig), Map_NodeIconData (NodeIconData).</t>
+          <t>※ UI: UI_Panel_MapPopup Prefab (Addressable). 노드 = Map_Node, 연결선 = Map_Line Prefab.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="20" t="inlineStr">
+        <is>
+          <t>※ Addressable Key: Map_GenerationConfig (RoomGenerationConfig), Map_NodeIconData (NodeIconData).</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>※ RoomType.Unknown은 초기화 전 기본값으로, 실제 노드에 배정되지 않으므로 표에서 제외했습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>※ Assets/Game/Core/Data/Map/MapGenerationConfig.asset은 스크립트 클래스 참조가 끊어진 고아 애셋(DeepEarth.Map.MapGenerationConfig 클래스 없음, Addressables 미등록)입니다. 실제 사용되는 애셋은 RoomGenerationConfig.asset이며 본 시트는 이를 기준으로 작성했습니다.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A17:G17"/>
+  <mergeCells count="3">
+    <mergeCell ref="A19:G19"/>
     <mergeCell ref="A18:G18"/>
-    <mergeCell ref="A20:G20"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A19:G19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/GameData/DataSheet.xlsx
+++ b/GameData/DataSheet.xlsx
@@ -10669,7 +10669,7 @@
         <v>0.8</v>
       </c>
       <c r="J4" s="16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K4" s="16" t="inlineStr">
         <is>
@@ -10678,7 +10678,7 @@
       </c>
       <c r="L4" s="25" t="inlineStr">
         <is>
-          <t>3마리 동시 스폰, 위치 오프셋 적용</t>
+          <t>2마리 동시 스폰, 위치 오프셋 적용</t>
         </is>
       </c>
       <c r="M4" s="16" t="n">
@@ -11584,7 +11584,6 @@
       <c r="F19" s="23" t="n"/>
       <c r="G19" s="24" t="n"/>
     </row>
-    <row r="20"/>
     <row r="21" ht="48" customHeight="1" s="21">
       <c r="A21" s="20" t="inlineStr">
         <is>
@@ -11630,8 +11629,8 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A19:G19"/>
+    <mergeCell ref="A2:G2"/>
     <mergeCell ref="A18:G18"/>
-    <mergeCell ref="A2:G2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/GameData/DataSheet.xlsx
+++ b/GameData/DataSheet.xlsx
@@ -10442,7 +10442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q15"/>
+  <dimension ref="A1:Q21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="12.75"/>
   <cols>
     <col width="30" customWidth="1" style="21" min="1" max="1"/>
@@ -10621,7 +10621,7 @@
         <v>50</v>
       </c>
       <c r="N3" s="14" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="O3" s="14" t="inlineStr">
         <is>
@@ -10685,13 +10685,15 @@
         <v>30</v>
       </c>
       <c r="N4" s="16" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="O4" s="16" t="n">
-        <v>15</v>
-      </c>
-      <c r="P4" s="16" t="n">
-        <v>15</v>
+        <v>10</v>
+      </c>
+      <c r="P4" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -10714,7 +10716,7 @@
         <v>2</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F5" s="14" t="n">
         <v>1</v>
@@ -10745,13 +10747,15 @@
         <v>20</v>
       </c>
       <c r="N5" s="14" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="O5" s="14" t="n">
-        <v>20</v>
-      </c>
-      <c r="P5" s="14" t="n">
-        <v>10</v>
+        <v>12</v>
+      </c>
+      <c r="P5" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -10807,13 +10811,15 @@
         </is>
       </c>
       <c r="N6" s="16" t="n">
+        <v>14</v>
+      </c>
+      <c r="O6" s="16" t="n">
         <v>20</v>
       </c>
-      <c r="O6" s="16" t="n">
-        <v>30</v>
-      </c>
-      <c r="P6" s="16" t="n">
-        <v>20</v>
+      <c r="P6" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="7" ht="25.5" customHeight="1" s="21">
@@ -10874,10 +10880,12 @@
         </is>
       </c>
       <c r="O7" s="14" t="n">
-        <v>25</v>
-      </c>
-      <c r="P7" s="14" t="n">
-        <v>35</v>
+        <v>18</v>
+      </c>
+      <c r="P7" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -10938,136 +10946,543 @@
         </is>
       </c>
       <c r="O8" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="P8" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="25" t="inlineStr">
+        <is>
+          <t>Combat_Monster_Spider</t>
+        </is>
+      </c>
+      <c r="B9" s="25" t="inlineStr">
+        <is>
+          <t>광석벌레</t>
+        </is>
+      </c>
+      <c r="C9" s="25" t="inlineStr">
+        <is>
+          <t>Ore Burrower</t>
+        </is>
+      </c>
+      <c r="D9" s="16" t="n">
+        <v>19</v>
+      </c>
+      <c r="E9" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="F9" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="H9" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J9" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L9" s="25" t="inlineStr">
+        <is>
+          <t>Special 사용마다 자기 공격력 -1(최대 2회 누적, 최소 1)</t>
+        </is>
+      </c>
+      <c r="M9" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N9" s="16" t="n">
+        <v>12</v>
+      </c>
+      <c r="O9" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P9" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="25.5" customHeight="1" s="21">
+      <c r="A10" s="25" t="inlineStr">
+        <is>
+          <t>Combat_Monster_Rat</t>
+        </is>
+      </c>
+      <c r="B10" s="25" t="inlineStr">
+        <is>
+          <t>수정박쥐</t>
+        </is>
+      </c>
+      <c r="C10" s="25" t="inlineStr">
+        <is>
+          <t>Crystal Bat</t>
+        </is>
+      </c>
+      <c r="D10" s="16" t="n">
+        <v>20</v>
+      </c>
+      <c r="E10" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="F10" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="H10" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J10" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L10" s="25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M10" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N10" s="16" t="n">
         <v>10</v>
       </c>
-      <c r="P8" s="16" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="22" t="inlineStr">
+      <c r="O10" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P10" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="25" t="inlineStr">
+        <is>
+          <t>Combat_Monster_Slime</t>
+        </is>
+      </c>
+      <c r="B11" s="25" t="inlineStr">
+        <is>
+          <t>광산 균사체</t>
+        </is>
+      </c>
+      <c r="C11" s="25" t="inlineStr">
+        <is>
+          <t>Mine Mycelium</t>
+        </is>
+      </c>
+      <c r="D11" s="16" t="n">
+        <v>21</v>
+      </c>
+      <c r="E11" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="F11" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="G11" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J11" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L11" s="25" t="inlineStr">
+        <is>
+          <t>공격 없음. Debuff 50%채굴력감소/50%공격력저하 1스택, Heal +2</t>
+        </is>
+      </c>
+      <c r="M11" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N11" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="O11" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P11" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="25" t="inlineStr">
+        <is>
+          <t>Combat_Monster_ArmoredSkeleton</t>
+        </is>
+      </c>
+      <c r="B12" s="25" t="inlineStr">
+        <is>
+          <t>석화 두더지</t>
+        </is>
+      </c>
+      <c r="C12" s="25" t="inlineStr">
+        <is>
+          <t>Petrified Mole</t>
+        </is>
+      </c>
+      <c r="D12" s="16" t="n">
+        <v>22</v>
+      </c>
+      <c r="E12" s="16" t="n">
+        <v>12</v>
+      </c>
+      <c r="F12" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="G12" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="H12" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="I12" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J12" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L12" s="25" t="inlineStr">
+        <is>
+          <t>Defend→HeavyAttack 2스텝 순환</t>
+        </is>
+      </c>
+      <c r="M12" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N12" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O12" s="16" t="n">
+        <v>12</v>
+      </c>
+      <c r="P12" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="25" t="inlineStr">
+        <is>
+          <t>Combat_Monster_Spider</t>
+        </is>
+      </c>
+      <c r="B13" s="25" t="inlineStr">
+        <is>
+          <t>심연의 광부벌</t>
+        </is>
+      </c>
+      <c r="C13" s="25" t="inlineStr">
+        <is>
+          <t>Abyss Miner Bee</t>
+        </is>
+      </c>
+      <c r="D13" s="16" t="n">
+        <v>23</v>
+      </c>
+      <c r="E13" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="F13" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="G13" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="H13" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J13" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L13" s="25" t="inlineStr">
+        <is>
+          <t>공격 적중 시 중독(3턴). Buff 사용 후 영구히 피격-30%+공격시30%확률 2배데미지</t>
+        </is>
+      </c>
+      <c r="M13" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N13" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O13" s="16" t="n">
+        <v>12</v>
+      </c>
+      <c r="P13" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="25" t="inlineStr">
+        <is>
+          <t>Combat_Monster_SmallSlime</t>
+        </is>
+      </c>
+      <c r="B14" s="25" t="inlineStr">
+        <is>
+          <t>황금광맥 정령</t>
+        </is>
+      </c>
+      <c r="C14" s="25" t="inlineStr">
+        <is>
+          <t>Gold Vein Spirit</t>
+        </is>
+      </c>
+      <c r="D14" s="16" t="n">
+        <v>24</v>
+      </c>
+      <c r="E14" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="F14" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="H14" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J14" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L14" s="25" t="inlineStr">
+        <is>
+          <t>공격력 = 기본 + Min(보유 Item_Gold, 10). Special로 다음 피격 1회 Min(1+골드,80)% 감소</t>
+        </is>
+      </c>
+      <c r="M14" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N14" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O14" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="P14" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="22" t="inlineStr">
         <is>
           <t>[분열 산물 - Slime 사망 시만 출현]</t>
         </is>
       </c>
-      <c r="B9" s="23" t="n"/>
-      <c r="C9" s="23" t="n"/>
-      <c r="D9" s="23" t="n"/>
-      <c r="E9" s="23" t="n"/>
-      <c r="F9" s="23" t="n"/>
-      <c r="G9" s="23" t="n"/>
-      <c r="H9" s="23" t="n"/>
-      <c r="I9" s="23" t="n"/>
-      <c r="J9" s="23" t="n"/>
-      <c r="K9" s="23" t="n"/>
-      <c r="L9" s="23" t="n"/>
-      <c r="M9" s="23" t="n"/>
-      <c r="N9" s="23" t="n"/>
-      <c r="O9" s="23" t="n"/>
-      <c r="P9" s="24" t="n"/>
-    </row>
-    <row r="10" ht="25.5" customHeight="1" s="21">
-      <c r="A10" s="26" t="inlineStr">
+      <c r="B15" s="23" t="n"/>
+      <c r="C15" s="23" t="n"/>
+      <c r="D15" s="23" t="n"/>
+      <c r="E15" s="23" t="n"/>
+      <c r="F15" s="23" t="n"/>
+      <c r="G15" s="23" t="n"/>
+      <c r="H15" s="23" t="n"/>
+      <c r="I15" s="23" t="n"/>
+      <c r="J15" s="23" t="n"/>
+      <c r="K15" s="23" t="n"/>
+      <c r="L15" s="23" t="n"/>
+      <c r="M15" s="23" t="n"/>
+      <c r="N15" s="23" t="n"/>
+      <c r="O15" s="23" t="n"/>
+      <c r="P15" s="24" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="26" t="inlineStr">
         <is>
           <t>Combat_Monster_SmallSlime</t>
         </is>
       </c>
-      <c r="B10" s="27" t="inlineStr">
+      <c r="B16" s="27" t="inlineStr">
         <is>
           <t>작은슬라임</t>
         </is>
       </c>
-      <c r="C10" s="26" t="inlineStr">
+      <c r="C16" s="26" t="inlineStr">
         <is>
           <t>Small Slime</t>
         </is>
       </c>
-      <c r="D10" s="14" t="n">
+      <c r="D16" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="E10" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="F10" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="14" t="n">
+      <c r="E16" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="H10" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" s="14" t="n">
+      <c r="F16" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" s="14" t="n">
         <v>0.8</v>
       </c>
-      <c r="J10" s="14" t="n">
+      <c r="J16" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="K10" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L10" s="26" t="inlineStr">
+      <c r="K16" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L16" s="26" t="inlineStr">
         <is>
           <t>Slime 사망 시 분열 산물, SpawnTable 직접 등록 없음</t>
         </is>
       </c>
-      <c r="M10" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N10" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O10" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P10" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="20" t="inlineStr">
+      <c r="M16" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N16" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O16" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P16" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="20" t="inlineStr">
         <is>
           <t>※ 난이도 스케일: depth&lt;50=tier1(+0), depth&lt;100=tier2(+1), depth&lt;200=tier3(+2), depth≥200=tier4(+3)</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="20" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="20" t="inlineStr">
         <is>
           <t>※ 최종HP = 기본HP + (HP/난이도 × (tier-1)),  최종데미지 = 기본데미지 + (데미지/난이도 × (tier-1))</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="20" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="20" t="inlineStr">
         <is>
           <t>※ 가중치 '-' = 해당 구간 미출현</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="20" t="inlineStr">
-        <is>
-          <t>※ 이 시트는 MonsterSpawnTable(일반 몬스터) 기준입니다. 엘리트 몬스터 6종(BigSlime/CursedKnight/CursedPriest/IronPlateSpider/MerchantMimic/SkeletonMiner, EliteSpawnTable 등록)과 보스 5종은 별도 시스템(EliteCombatSystem/BossManager)으로 관리되며 이 시트에는 포함되지 않습니다.</t>
+    <row r="21">
+      <c r="A21" s="20" t="inlineStr">
+        <is>
+          <t>※ 이 시트는 MonsterSpawnTable(일반 몬스터) 기준입니다. 엘리트 몬스터 9종(BigSlime/CursedKnight/CursedPriest/IronPlateSpider/MerchantMimic/SkeletonMiner/MagmaLizard/CrystalSerpent/FossilTroll, EliteSpawnTable 등록)과 보스 5종은 별도 시스템(EliteCombatSystem/BossManager)으로 관리되며 이 시트에는 포함되지 않습니다. 2026-08-16부터 진행 구조가 3단계(깊이 150 종료)로 축소되어 깊이 200+ 구간은 게임상 도달 불가능하다 — 아래 D200+ 열은 전부 "-"이며, D100-199 열이 사실상 "100+ 전체"를 의미한다.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A13:P13"/>
-    <mergeCell ref="A14:P14"/>
-    <mergeCell ref="A9:P9"/>
-    <mergeCell ref="A12:P12"/>
+  <mergeCells count="2">
+    <mergeCell ref="A15:P15"/>
     <mergeCell ref="A2:P2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
